--- a/frontend/public/external/OSG NSA List of participants (20250401).xlsx
+++ b/frontend/public/external/OSG NSA List of participants (20250401).xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <fileSharing readOnlyRecommended="1"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Moses Lee\Desktop\Github\ecss-cms\frontend\public\external\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/moseslee/Desktop/ecss-cms/frontend/public/external/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE278C5-6BCB-425C-BCD1-6EFF34990190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DE4FFC-940E-3145-B84B-B9CDF44EE8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LOP" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">LOP!$A$8:$Z$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">LOP!$A$1:$AA$143</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">LOP!$A$1:$AA$49</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">LOP!$7:$8</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -1175,6 +1175,33 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1200,35 +1227,8 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -1836,35 +1836,35 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD153"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AD59"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="37.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="43" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="1" customWidth="1"/>
-    <col min="8" max="9" width="20.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="23.42578125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="29.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="22.85546875" style="1" customWidth="1"/>
-    <col min="15" max="20" width="35.140625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="26.5703125" style="1" customWidth="1"/>
-    <col min="22" max="22" width="22.85546875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="22.7109375" style="1" customWidth="1"/>
-    <col min="24" max="24" width="35.42578125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="20.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="29.5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="22.83203125" style="1" customWidth="1"/>
+    <col min="15" max="20" width="35.1640625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="26.5" style="1" customWidth="1"/>
+    <col min="22" max="22" width="22.83203125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="22.6640625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="35.5" style="1" customWidth="1"/>
     <col min="25" max="25" width="23" style="1" customWidth="1"/>
-    <col min="26" max="26" width="25.140625" style="1" customWidth="1"/>
-    <col min="27" max="29" width="21.42578125" customWidth="1"/>
-    <col min="30" max="30" width="37.7109375" style="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="26" max="26" width="25.1640625" style="1" customWidth="1"/>
+    <col min="27" max="29" width="21.5" customWidth="1"/>
+    <col min="30" max="30" width="37.6640625" style="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>15</v>
       </c>
@@ -1873,12 +1873,12 @@
       <c r="AB1"/>
       <c r="AC1"/>
     </row>
-    <row r="2" spans="1:30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
     </row>
-    <row r="3" spans="1:30" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>13</v>
       </c>
@@ -1911,7 +1911,7 @@
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
     </row>
-    <row r="4" spans="1:30" ht="25.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" ht="25.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>4</v>
       </c>
@@ -1947,7 +1947,7 @@
       <c r="AB4" s="2"/>
       <c r="AC4" s="1"/>
     </row>
-    <row r="5" spans="1:30" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>5</v>
       </c>
@@ -1996,7 +1996,7 @@
       <c r="AB5" s="2"/>
       <c r="AC5" s="1"/>
     </row>
-    <row r="6" spans="1:30" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
         <v>43</v>
       </c>
@@ -2031,7 +2031,7 @@
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
     </row>
-    <row r="7" spans="1:30" s="9" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" s="9" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="97" t="s">
         <v>16</v>
       </c>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="AC7" s="92"/>
     </row>
-    <row r="8" spans="1:30" s="2" customFormat="1" ht="58.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" s="2" customFormat="1" ht="58.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>2</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="21"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
@@ -2196,7 +2196,7 @@
       <c r="AC9" s="30"/>
       <c r="AD9" s="21"/>
     </row>
-    <row r="10" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="21"/>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
@@ -2228,7 +2228,7 @@
       <c r="AC10" s="30"/>
       <c r="AD10" s="21"/>
     </row>
-    <row r="11" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="21"/>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
@@ -2260,7 +2260,7 @@
       <c r="AC11" s="30"/>
       <c r="AD11" s="21"/>
     </row>
-    <row r="12" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="21"/>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -2292,7 +2292,7 @@
       <c r="AC12" s="30"/>
       <c r="AD12" s="21"/>
     </row>
-    <row r="13" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="21"/>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -2324,7 +2324,7 @@
       <c r="AC13" s="30"/>
       <c r="AD13" s="21"/>
     </row>
-    <row r="14" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
@@ -2356,7 +2356,7 @@
       <c r="AC14" s="30"/>
       <c r="AD14" s="21"/>
     </row>
-    <row r="15" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="21"/>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
@@ -2388,7 +2388,7 @@
       <c r="AC15" s="30"/>
       <c r="AD15" s="21"/>
     </row>
-    <row r="16" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="21"/>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
@@ -2420,7 +2420,7 @@
       <c r="AC16" s="30"/>
       <c r="AD16" s="21"/>
     </row>
-    <row r="17" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="21"/>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
@@ -2452,7 +2452,7 @@
       <c r="AC17" s="30"/>
       <c r="AD17" s="21"/>
     </row>
-    <row r="18" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="21"/>
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
@@ -2484,7 +2484,7 @@
       <c r="AC18" s="30"/>
       <c r="AD18" s="21"/>
     </row>
-    <row r="19" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21"/>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -2516,7 +2516,7 @@
       <c r="AC19" s="30"/>
       <c r="AD19" s="21"/>
     </row>
-    <row r="20" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="21"/>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
@@ -2548,7 +2548,7 @@
       <c r="AC20" s="30"/>
       <c r="AD20" s="21"/>
     </row>
-    <row r="21" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -2580,7 +2580,7 @@
       <c r="AC21" s="30"/>
       <c r="AD21" s="21"/>
     </row>
-    <row r="22" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="21"/>
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
@@ -2612,7 +2612,7 @@
       <c r="AC22" s="30"/>
       <c r="AD22" s="21"/>
     </row>
-    <row r="23" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="21"/>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
@@ -2644,7 +2644,7 @@
       <c r="AC23" s="30"/>
       <c r="AD23" s="21"/>
     </row>
-    <row r="24" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="21"/>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
@@ -2676,7 +2676,7 @@
       <c r="AC24" s="30"/>
       <c r="AD24" s="21"/>
     </row>
-    <row r="25" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="21"/>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
@@ -2708,7 +2708,7 @@
       <c r="AC25" s="30"/>
       <c r="AD25" s="21"/>
     </row>
-    <row r="26" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="21"/>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -2740,7 +2740,7 @@
       <c r="AC26" s="30"/>
       <c r="AD26" s="21"/>
     </row>
-    <row r="27" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="21"/>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -2772,7 +2772,7 @@
       <c r="AC27" s="30"/>
       <c r="AD27" s="21"/>
     </row>
-    <row r="28" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="21"/>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -2804,7 +2804,7 @@
       <c r="AC28" s="30"/>
       <c r="AD28" s="21"/>
     </row>
-    <row r="29" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="21"/>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -2836,7 +2836,7 @@
       <c r="AC29" s="30"/>
       <c r="AD29" s="21"/>
     </row>
-    <row r="30" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="21"/>
       <c r="B30" s="21"/>
       <c r="C30" s="21"/>
@@ -2868,7 +2868,7 @@
       <c r="AC30" s="30"/>
       <c r="AD30" s="21"/>
     </row>
-    <row r="31" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="21"/>
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
@@ -2900,7 +2900,7 @@
       <c r="AC31" s="30"/>
       <c r="AD31" s="21"/>
     </row>
-    <row r="32" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="21"/>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -2932,7 +2932,7 @@
       <c r="AC32" s="30"/>
       <c r="AD32" s="21"/>
     </row>
-    <row r="33" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="21"/>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -2964,7 +2964,7 @@
       <c r="AC33" s="30"/>
       <c r="AD33" s="21"/>
     </row>
-    <row r="34" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="21"/>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
@@ -2996,7 +2996,7 @@
       <c r="AC34" s="30"/>
       <c r="AD34" s="21"/>
     </row>
-    <row r="35" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="21"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
@@ -3028,7 +3028,7 @@
       <c r="AC35" s="30"/>
       <c r="AD35" s="21"/>
     </row>
-    <row r="36" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
@@ -3060,7 +3060,7 @@
       <c r="AC36" s="30"/>
       <c r="AD36" s="21"/>
     </row>
-    <row r="37" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="21"/>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
@@ -3092,7 +3092,7 @@
       <c r="AC37" s="30"/>
       <c r="AD37" s="21"/>
     </row>
-    <row r="38" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="21"/>
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
@@ -3124,7 +3124,7 @@
       <c r="AC38" s="30"/>
       <c r="AD38" s="21"/>
     </row>
-    <row r="39" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="21"/>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
@@ -3156,7 +3156,7 @@
       <c r="AC39" s="30"/>
       <c r="AD39" s="21"/>
     </row>
-    <row r="40" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="21"/>
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
@@ -3188,7 +3188,7 @@
       <c r="AC40" s="30"/>
       <c r="AD40" s="21"/>
     </row>
-    <row r="41" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="21"/>
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
@@ -3220,7 +3220,7 @@
       <c r="AC41" s="30"/>
       <c r="AD41" s="21"/>
     </row>
-    <row r="42" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="21"/>
       <c r="B42" s="21"/>
       <c r="C42" s="21"/>
@@ -3252,7 +3252,7 @@
       <c r="AC42" s="30"/>
       <c r="AD42" s="21"/>
     </row>
-    <row r="43" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="21"/>
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
@@ -3284,7 +3284,7 @@
       <c r="AC43" s="30"/>
       <c r="AD43" s="21"/>
     </row>
-    <row r="44" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="21"/>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
@@ -3316,7 +3316,7 @@
       <c r="AC44" s="30"/>
       <c r="AD44" s="21"/>
     </row>
-    <row r="45" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
@@ -3348,7 +3348,7 @@
       <c r="AC45" s="30"/>
       <c r="AD45" s="21"/>
     </row>
-    <row r="46" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
@@ -3380,7 +3380,7 @@
       <c r="AC46" s="30"/>
       <c r="AD46" s="21"/>
     </row>
-    <row r="47" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
@@ -3412,7 +3412,7 @@
       <c r="AC47" s="30"/>
       <c r="AD47" s="21"/>
     </row>
-    <row r="48" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" s="20" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="21"/>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
@@ -3444,3042 +3444,34 @@
       <c r="AC48" s="30"/>
       <c r="AD48" s="21"/>
     </row>
-    <row r="49" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="21"/>
-      <c r="B49" s="21"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="85"/>
-      <c r="F49" s="85"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="21"/>
-      <c r="J49" s="21"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="85"/>
-      <c r="M49" s="23"/>
-      <c r="N49" s="86"/>
-      <c r="O49" s="23"/>
-      <c r="P49" s="23"/>
-      <c r="Q49" s="23"/>
-      <c r="R49" s="23"/>
-      <c r="S49" s="23"/>
-      <c r="T49" s="23"/>
-      <c r="U49" s="24"/>
-      <c r="V49" s="24"/>
-      <c r="W49" s="88"/>
-      <c r="X49" s="88"/>
-      <c r="Y49" s="88"/>
-      <c r="Z49" s="88"/>
-      <c r="AA49" s="89"/>
-      <c r="AB49" s="30"/>
-      <c r="AC49" s="30"/>
-      <c r="AD49" s="21"/>
-    </row>
-    <row r="50" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="21"/>
-      <c r="B50" s="21"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="85"/>
-      <c r="F50" s="85"/>
-      <c r="G50" s="21"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="21"/>
-      <c r="K50" s="23"/>
-      <c r="L50" s="85"/>
-      <c r="M50" s="23"/>
-      <c r="N50" s="86"/>
-      <c r="O50" s="23"/>
-      <c r="P50" s="23"/>
-      <c r="Q50" s="23"/>
-      <c r="R50" s="23"/>
-      <c r="S50" s="23"/>
-      <c r="T50" s="23"/>
-      <c r="U50" s="24"/>
-      <c r="V50" s="24"/>
-      <c r="W50" s="88"/>
-      <c r="X50" s="88"/>
-      <c r="Y50" s="88"/>
-      <c r="Z50" s="88"/>
-      <c r="AA50" s="89"/>
-      <c r="AB50" s="30"/>
-      <c r="AC50" s="30"/>
-      <c r="AD50" s="21"/>
-    </row>
-    <row r="51" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="21"/>
-      <c r="B51" s="21"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="85"/>
-      <c r="F51" s="85"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
-      <c r="K51" s="23"/>
-      <c r="L51" s="85"/>
-      <c r="M51" s="23"/>
-      <c r="N51" s="86"/>
-      <c r="O51" s="23"/>
-      <c r="P51" s="23"/>
-      <c r="Q51" s="23"/>
-      <c r="R51" s="23"/>
-      <c r="S51" s="23"/>
-      <c r="T51" s="23"/>
-      <c r="U51" s="24"/>
-      <c r="V51" s="24"/>
-      <c r="W51" s="88"/>
-      <c r="X51" s="88"/>
-      <c r="Y51" s="88"/>
-      <c r="Z51" s="88"/>
-      <c r="AA51" s="89"/>
-      <c r="AB51" s="30"/>
-      <c r="AC51" s="30"/>
-      <c r="AD51" s="21"/>
-    </row>
-    <row r="52" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="21"/>
-      <c r="B52" s="21"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="85"/>
-      <c r="F52" s="85"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
-      <c r="J52" s="21"/>
-      <c r="K52" s="23"/>
-      <c r="L52" s="85"/>
-      <c r="M52" s="23"/>
-      <c r="N52" s="86"/>
-      <c r="O52" s="23"/>
-      <c r="P52" s="23"/>
-      <c r="Q52" s="23"/>
-      <c r="R52" s="23"/>
-      <c r="S52" s="23"/>
-      <c r="T52" s="23"/>
-      <c r="U52" s="24"/>
-      <c r="V52" s="24"/>
-      <c r="W52" s="88"/>
-      <c r="X52" s="88"/>
-      <c r="Y52" s="88"/>
-      <c r="Z52" s="88"/>
-      <c r="AA52" s="89"/>
-      <c r="AB52" s="30"/>
-      <c r="AC52" s="30"/>
-      <c r="AD52" s="21"/>
-    </row>
-    <row r="53" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="85"/>
-      <c r="F53" s="85"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="21"/>
-      <c r="J53" s="21"/>
-      <c r="K53" s="23"/>
-      <c r="L53" s="85"/>
-      <c r="M53" s="23"/>
-      <c r="N53" s="86"/>
-      <c r="O53" s="23"/>
-      <c r="P53" s="23"/>
-      <c r="Q53" s="23"/>
-      <c r="R53" s="23"/>
-      <c r="S53" s="23"/>
-      <c r="T53" s="23"/>
-      <c r="U53" s="24"/>
-      <c r="V53" s="24"/>
-      <c r="W53" s="88"/>
-      <c r="X53" s="88"/>
-      <c r="Y53" s="88"/>
-      <c r="Z53" s="88"/>
-      <c r="AA53" s="89"/>
-      <c r="AB53" s="30"/>
-      <c r="AC53" s="30"/>
-      <c r="AD53" s="21"/>
-    </row>
-    <row r="54" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="85"/>
-      <c r="F54" s="85"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
-      <c r="J54" s="21"/>
-      <c r="K54" s="23"/>
-      <c r="L54" s="85"/>
-      <c r="M54" s="23"/>
-      <c r="N54" s="86"/>
-      <c r="O54" s="23"/>
-      <c r="P54" s="23"/>
-      <c r="Q54" s="23"/>
-      <c r="R54" s="23"/>
-      <c r="S54" s="23"/>
-      <c r="T54" s="23"/>
-      <c r="U54" s="24"/>
-      <c r="V54" s="24"/>
-      <c r="W54" s="88"/>
-      <c r="X54" s="88"/>
-      <c r="Y54" s="88"/>
-      <c r="Z54" s="88"/>
-      <c r="AA54" s="89"/>
-      <c r="AB54" s="30"/>
-      <c r="AC54" s="30"/>
-      <c r="AD54" s="21"/>
-    </row>
-    <row r="55" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="21"/>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="85"/>
-      <c r="F55" s="85"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
-      <c r="J55" s="21"/>
-      <c r="K55" s="23"/>
-      <c r="L55" s="85"/>
-      <c r="M55" s="23"/>
-      <c r="N55" s="86"/>
-      <c r="O55" s="23"/>
-      <c r="P55" s="23"/>
-      <c r="Q55" s="23"/>
-      <c r="R55" s="23"/>
-      <c r="S55" s="23"/>
-      <c r="T55" s="23"/>
-      <c r="U55" s="24"/>
-      <c r="V55" s="24"/>
-      <c r="W55" s="88"/>
-      <c r="X55" s="88"/>
-      <c r="Y55" s="88"/>
-      <c r="Z55" s="88"/>
-      <c r="AA55" s="89"/>
-      <c r="AB55" s="30"/>
-      <c r="AC55" s="30"/>
-      <c r="AD55" s="21"/>
-    </row>
-    <row r="56" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21"/>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="85"/>
-      <c r="F56" s="85"/>
-      <c r="G56" s="21"/>
-      <c r="H56" s="21"/>
-      <c r="I56" s="21"/>
-      <c r="J56" s="21"/>
-      <c r="K56" s="23"/>
-      <c r="L56" s="85"/>
-      <c r="M56" s="23"/>
-      <c r="N56" s="86"/>
-      <c r="O56" s="23"/>
-      <c r="P56" s="23"/>
-      <c r="Q56" s="23"/>
-      <c r="R56" s="23"/>
-      <c r="S56" s="23"/>
-      <c r="T56" s="23"/>
-      <c r="U56" s="24"/>
-      <c r="V56" s="24"/>
-      <c r="W56" s="88"/>
-      <c r="X56" s="88"/>
-      <c r="Y56" s="88"/>
-      <c r="Z56" s="88"/>
-      <c r="AA56" s="89"/>
-      <c r="AB56" s="30"/>
-      <c r="AC56" s="30"/>
-      <c r="AD56" s="21"/>
-    </row>
-    <row r="57" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="21"/>
-      <c r="B57" s="21"/>
-      <c r="C57" s="21"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="85"/>
-      <c r="F57" s="85"/>
-      <c r="G57" s="21"/>
-      <c r="H57" s="21"/>
-      <c r="I57" s="21"/>
-      <c r="J57" s="21"/>
-      <c r="K57" s="23"/>
-      <c r="L57" s="85"/>
-      <c r="M57" s="23"/>
-      <c r="N57" s="86"/>
-      <c r="O57" s="23"/>
-      <c r="P57" s="23"/>
-      <c r="Q57" s="23"/>
-      <c r="R57" s="23"/>
-      <c r="S57" s="23"/>
-      <c r="T57" s="23"/>
-      <c r="U57" s="24"/>
-      <c r="V57" s="24"/>
-      <c r="W57" s="88"/>
-      <c r="X57" s="88"/>
-      <c r="Y57" s="88"/>
-      <c r="Z57" s="88"/>
-      <c r="AA57" s="89"/>
-      <c r="AB57" s="30"/>
-      <c r="AC57" s="30"/>
-      <c r="AD57" s="21"/>
-    </row>
-    <row r="58" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="21"/>
-      <c r="B58" s="21"/>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="85"/>
-      <c r="F58" s="85"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
-      <c r="J58" s="21"/>
-      <c r="K58" s="23"/>
-      <c r="L58" s="85"/>
-      <c r="M58" s="23"/>
-      <c r="N58" s="86"/>
-      <c r="O58" s="23"/>
-      <c r="P58" s="23"/>
-      <c r="Q58" s="23"/>
-      <c r="R58" s="23"/>
-      <c r="S58" s="23"/>
-      <c r="T58" s="23"/>
-      <c r="U58" s="24"/>
-      <c r="V58" s="24"/>
-      <c r="W58" s="88"/>
-      <c r="X58" s="88"/>
-      <c r="Y58" s="88"/>
-      <c r="Z58" s="88"/>
-      <c r="AA58" s="89"/>
-      <c r="AB58" s="30"/>
-      <c r="AC58" s="30"/>
-      <c r="AD58" s="21"/>
-    </row>
-    <row r="59" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="21"/>
-      <c r="B59" s="21"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="85"/>
-      <c r="F59" s="85"/>
-      <c r="G59" s="21"/>
-      <c r="H59" s="21"/>
-      <c r="I59" s="21"/>
-      <c r="J59" s="21"/>
-      <c r="K59" s="23"/>
-      <c r="L59" s="85"/>
-      <c r="M59" s="23"/>
-      <c r="N59" s="86"/>
-      <c r="O59" s="23"/>
-      <c r="P59" s="23"/>
-      <c r="Q59" s="23"/>
-      <c r="R59" s="23"/>
-      <c r="S59" s="23"/>
-      <c r="T59" s="23"/>
-      <c r="U59" s="24"/>
-      <c r="V59" s="24"/>
-      <c r="W59" s="88"/>
-      <c r="X59" s="88"/>
-      <c r="Y59" s="88"/>
-      <c r="Z59" s="88"/>
-      <c r="AA59" s="89"/>
-      <c r="AB59" s="30"/>
-      <c r="AC59" s="30"/>
-      <c r="AD59" s="21"/>
-    </row>
-    <row r="60" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="85"/>
-      <c r="F60" s="85"/>
-      <c r="G60" s="21"/>
-      <c r="H60" s="21"/>
-      <c r="I60" s="21"/>
-      <c r="J60" s="21"/>
-      <c r="K60" s="23"/>
-      <c r="L60" s="85"/>
-      <c r="M60" s="23"/>
-      <c r="N60" s="86"/>
-      <c r="O60" s="23"/>
-      <c r="P60" s="23"/>
-      <c r="Q60" s="23"/>
-      <c r="R60" s="23"/>
-      <c r="S60" s="23"/>
-      <c r="T60" s="23"/>
-      <c r="U60" s="24"/>
-      <c r="V60" s="24"/>
-      <c r="W60" s="88"/>
-      <c r="X60" s="88"/>
-      <c r="Y60" s="88"/>
-      <c r="Z60" s="88"/>
-      <c r="AA60" s="89"/>
-      <c r="AB60" s="30"/>
-      <c r="AC60" s="30"/>
-      <c r="AD60" s="21"/>
-    </row>
-    <row r="61" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="21"/>
-      <c r="B61" s="21"/>
-      <c r="C61" s="21"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="85"/>
-      <c r="F61" s="85"/>
-      <c r="G61" s="21"/>
-      <c r="H61" s="21"/>
-      <c r="I61" s="21"/>
-      <c r="J61" s="21"/>
-      <c r="K61" s="23"/>
-      <c r="L61" s="85"/>
-      <c r="M61" s="23"/>
-      <c r="N61" s="86"/>
-      <c r="O61" s="23"/>
-      <c r="P61" s="23"/>
-      <c r="Q61" s="23"/>
-      <c r="R61" s="23"/>
-      <c r="S61" s="23"/>
-      <c r="T61" s="23"/>
-      <c r="U61" s="24"/>
-      <c r="V61" s="24"/>
-      <c r="W61" s="88"/>
-      <c r="X61" s="88"/>
-      <c r="Y61" s="88"/>
-      <c r="Z61" s="88"/>
-      <c r="AA61" s="89"/>
-      <c r="AB61" s="30"/>
-      <c r="AC61" s="30"/>
-      <c r="AD61" s="21"/>
-    </row>
-    <row r="62" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="21"/>
-      <c r="B62" s="21"/>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="85"/>
-      <c r="F62" s="85"/>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21"/>
-      <c r="I62" s="21"/>
-      <c r="J62" s="21"/>
-      <c r="K62" s="23"/>
-      <c r="L62" s="85"/>
-      <c r="M62" s="23"/>
-      <c r="N62" s="86"/>
-      <c r="O62" s="23"/>
-      <c r="P62" s="23"/>
-      <c r="Q62" s="23"/>
-      <c r="R62" s="23"/>
-      <c r="S62" s="23"/>
-      <c r="T62" s="23"/>
-      <c r="U62" s="24"/>
-      <c r="V62" s="24"/>
-      <c r="W62" s="88"/>
-      <c r="X62" s="88"/>
-      <c r="Y62" s="88"/>
-      <c r="Z62" s="88"/>
-      <c r="AA62" s="89"/>
-      <c r="AB62" s="30"/>
-      <c r="AC62" s="30"/>
-      <c r="AD62" s="21"/>
-    </row>
-    <row r="63" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="21"/>
-      <c r="B63" s="21"/>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="85"/>
-      <c r="F63" s="85"/>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21"/>
-      <c r="I63" s="21"/>
-      <c r="J63" s="21"/>
-      <c r="K63" s="23"/>
-      <c r="L63" s="85"/>
-      <c r="M63" s="23"/>
-      <c r="N63" s="86"/>
-      <c r="O63" s="23"/>
-      <c r="P63" s="23"/>
-      <c r="Q63" s="23"/>
-      <c r="R63" s="23"/>
-      <c r="S63" s="23"/>
-      <c r="T63" s="23"/>
-      <c r="U63" s="24"/>
-      <c r="V63" s="24"/>
-      <c r="W63" s="88"/>
-      <c r="X63" s="88"/>
-      <c r="Y63" s="88"/>
-      <c r="Z63" s="88"/>
-      <c r="AA63" s="89"/>
-      <c r="AB63" s="30"/>
-      <c r="AC63" s="30"/>
-      <c r="AD63" s="21"/>
-    </row>
-    <row r="64" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="21"/>
-      <c r="B64" s="21"/>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="85"/>
-      <c r="F64" s="85"/>
-      <c r="G64" s="21"/>
-      <c r="H64" s="21"/>
-      <c r="I64" s="21"/>
-      <c r="J64" s="21"/>
-      <c r="K64" s="23"/>
-      <c r="L64" s="85"/>
-      <c r="M64" s="23"/>
-      <c r="N64" s="86"/>
-      <c r="O64" s="23"/>
-      <c r="P64" s="23"/>
-      <c r="Q64" s="23"/>
-      <c r="R64" s="23"/>
-      <c r="S64" s="23"/>
-      <c r="T64" s="23"/>
-      <c r="U64" s="24"/>
-      <c r="V64" s="24"/>
-      <c r="W64" s="88"/>
-      <c r="X64" s="88"/>
-      <c r="Y64" s="88"/>
-      <c r="Z64" s="88"/>
-      <c r="AA64" s="89"/>
-      <c r="AB64" s="30"/>
-      <c r="AC64" s="30"/>
-      <c r="AD64" s="21"/>
-    </row>
-    <row r="65" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="21"/>
-      <c r="B65" s="21"/>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="85"/>
-      <c r="F65" s="85"/>
-      <c r="G65" s="21"/>
-      <c r="H65" s="21"/>
-      <c r="I65" s="21"/>
-      <c r="J65" s="21"/>
-      <c r="K65" s="23"/>
-      <c r="L65" s="85"/>
-      <c r="M65" s="23"/>
-      <c r="N65" s="86"/>
-      <c r="O65" s="23"/>
-      <c r="P65" s="23"/>
-      <c r="Q65" s="23"/>
-      <c r="R65" s="23"/>
-      <c r="S65" s="23"/>
-      <c r="T65" s="23"/>
-      <c r="U65" s="24"/>
-      <c r="V65" s="24"/>
-      <c r="W65" s="88"/>
-      <c r="X65" s="88"/>
-      <c r="Y65" s="88"/>
-      <c r="Z65" s="88"/>
-      <c r="AA65" s="89"/>
-      <c r="AB65" s="30"/>
-      <c r="AC65" s="30"/>
-      <c r="AD65" s="21"/>
-    </row>
-    <row r="66" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="21"/>
-      <c r="B66" s="21"/>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="85"/>
-      <c r="F66" s="85"/>
-      <c r="G66" s="21"/>
-      <c r="H66" s="21"/>
-      <c r="I66" s="21"/>
-      <c r="J66" s="21"/>
-      <c r="K66" s="23"/>
-      <c r="L66" s="85"/>
-      <c r="M66" s="23"/>
-      <c r="N66" s="86"/>
-      <c r="O66" s="23"/>
-      <c r="P66" s="23"/>
-      <c r="Q66" s="23"/>
-      <c r="R66" s="23"/>
-      <c r="S66" s="23"/>
-      <c r="T66" s="23"/>
-      <c r="U66" s="24"/>
-      <c r="V66" s="24"/>
-      <c r="W66" s="88"/>
-      <c r="X66" s="88"/>
-      <c r="Y66" s="88"/>
-      <c r="Z66" s="88"/>
-      <c r="AA66" s="89"/>
-      <c r="AB66" s="30"/>
-      <c r="AC66" s="30"/>
-      <c r="AD66" s="21"/>
-    </row>
-    <row r="67" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="21"/>
-      <c r="B67" s="21"/>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="85"/>
-      <c r="F67" s="85"/>
-      <c r="G67" s="21"/>
-      <c r="H67" s="21"/>
-      <c r="I67" s="21"/>
-      <c r="J67" s="21"/>
-      <c r="K67" s="23"/>
-      <c r="L67" s="85"/>
-      <c r="M67" s="23"/>
-      <c r="N67" s="86"/>
-      <c r="O67" s="23"/>
-      <c r="P67" s="23"/>
-      <c r="Q67" s="23"/>
-      <c r="R67" s="23"/>
-      <c r="S67" s="23"/>
-      <c r="T67" s="23"/>
-      <c r="U67" s="24"/>
-      <c r="V67" s="24"/>
-      <c r="W67" s="88"/>
-      <c r="X67" s="88"/>
-      <c r="Y67" s="88"/>
-      <c r="Z67" s="88"/>
-      <c r="AA67" s="89"/>
-      <c r="AB67" s="30"/>
-      <c r="AC67" s="30"/>
-      <c r="AD67" s="21"/>
-    </row>
-    <row r="68" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="21"/>
-      <c r="B68" s="21"/>
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="85"/>
-      <c r="F68" s="85"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="23"/>
-      <c r="L68" s="85"/>
-      <c r="M68" s="23"/>
-      <c r="N68" s="86"/>
-      <c r="O68" s="23"/>
-      <c r="P68" s="23"/>
-      <c r="Q68" s="23"/>
-      <c r="R68" s="23"/>
-      <c r="S68" s="23"/>
-      <c r="T68" s="23"/>
-      <c r="U68" s="24"/>
-      <c r="V68" s="24"/>
-      <c r="W68" s="88"/>
-      <c r="X68" s="88"/>
-      <c r="Y68" s="88"/>
-      <c r="Z68" s="88"/>
-      <c r="AA68" s="89"/>
-      <c r="AB68" s="30"/>
-      <c r="AC68" s="30"/>
-      <c r="AD68" s="21"/>
-    </row>
-    <row r="69" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="21"/>
-      <c r="B69" s="21"/>
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="85"/>
-      <c r="F69" s="85"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="21"/>
-      <c r="K69" s="23"/>
-      <c r="L69" s="85"/>
-      <c r="M69" s="23"/>
-      <c r="N69" s="86"/>
-      <c r="O69" s="23"/>
-      <c r="P69" s="23"/>
-      <c r="Q69" s="23"/>
-      <c r="R69" s="23"/>
-      <c r="S69" s="23"/>
-      <c r="T69" s="23"/>
-      <c r="U69" s="24"/>
-      <c r="V69" s="24"/>
-      <c r="W69" s="88"/>
-      <c r="X69" s="88"/>
-      <c r="Y69" s="88"/>
-      <c r="Z69" s="88"/>
-      <c r="AA69" s="89"/>
-      <c r="AB69" s="30"/>
-      <c r="AC69" s="30"/>
-      <c r="AD69" s="21"/>
-    </row>
-    <row r="70" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="21"/>
-      <c r="B70" s="21"/>
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="85"/>
-      <c r="F70" s="85"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="21"/>
-      <c r="I70" s="21"/>
-      <c r="J70" s="21"/>
-      <c r="K70" s="23"/>
-      <c r="L70" s="85"/>
-      <c r="M70" s="23"/>
-      <c r="N70" s="86"/>
-      <c r="O70" s="23"/>
-      <c r="P70" s="23"/>
-      <c r="Q70" s="23"/>
-      <c r="R70" s="23"/>
-      <c r="S70" s="23"/>
-      <c r="T70" s="23"/>
-      <c r="U70" s="24"/>
-      <c r="V70" s="24"/>
-      <c r="W70" s="88"/>
-      <c r="X70" s="88"/>
-      <c r="Y70" s="88"/>
-      <c r="Z70" s="88"/>
-      <c r="AA70" s="89"/>
-      <c r="AB70" s="30"/>
-      <c r="AC70" s="30"/>
-      <c r="AD70" s="21"/>
-    </row>
-    <row r="71" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="21"/>
-      <c r="B71" s="21"/>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="85"/>
-      <c r="F71" s="85"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="23"/>
-      <c r="L71" s="85"/>
-      <c r="M71" s="23"/>
-      <c r="N71" s="86"/>
-      <c r="O71" s="23"/>
-      <c r="P71" s="23"/>
-      <c r="Q71" s="23"/>
-      <c r="R71" s="23"/>
-      <c r="S71" s="23"/>
-      <c r="T71" s="23"/>
-      <c r="U71" s="24"/>
-      <c r="V71" s="24"/>
-      <c r="W71" s="88"/>
-      <c r="X71" s="88"/>
-      <c r="Y71" s="88"/>
-      <c r="Z71" s="88"/>
-      <c r="AA71" s="89"/>
-      <c r="AB71" s="30"/>
-      <c r="AC71" s="30"/>
-      <c r="AD71" s="21"/>
-    </row>
-    <row r="72" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="21"/>
-      <c r="B72" s="21"/>
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="85"/>
-      <c r="F72" s="85"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21"/>
-      <c r="K72" s="23"/>
-      <c r="L72" s="85"/>
-      <c r="M72" s="23"/>
-      <c r="N72" s="86"/>
-      <c r="O72" s="23"/>
-      <c r="P72" s="23"/>
-      <c r="Q72" s="23"/>
-      <c r="R72" s="23"/>
-      <c r="S72" s="23"/>
-      <c r="T72" s="23"/>
-      <c r="U72" s="24"/>
-      <c r="V72" s="24"/>
-      <c r="W72" s="88"/>
-      <c r="X72" s="88"/>
-      <c r="Y72" s="88"/>
-      <c r="Z72" s="88"/>
-      <c r="AA72" s="89"/>
-      <c r="AB72" s="30"/>
-      <c r="AC72" s="30"/>
-      <c r="AD72" s="21"/>
-    </row>
-    <row r="73" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="21"/>
-      <c r="B73" s="21"/>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="85"/>
-      <c r="F73" s="85"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-      <c r="K73" s="23"/>
-      <c r="L73" s="85"/>
-      <c r="M73" s="23"/>
-      <c r="N73" s="86"/>
-      <c r="O73" s="23"/>
-      <c r="P73" s="23"/>
-      <c r="Q73" s="23"/>
-      <c r="R73" s="23"/>
-      <c r="S73" s="23"/>
-      <c r="T73" s="23"/>
-      <c r="U73" s="24"/>
-      <c r="V73" s="24"/>
-      <c r="W73" s="88"/>
-      <c r="X73" s="88"/>
-      <c r="Y73" s="88"/>
-      <c r="Z73" s="88"/>
-      <c r="AA73" s="89"/>
-      <c r="AB73" s="30"/>
-      <c r="AC73" s="30"/>
-      <c r="AD73" s="21"/>
-    </row>
-    <row r="74" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="21"/>
-      <c r="B74" s="21"/>
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="85"/>
-      <c r="F74" s="85"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="23"/>
-      <c r="L74" s="85"/>
-      <c r="M74" s="23"/>
-      <c r="N74" s="86"/>
-      <c r="O74" s="23"/>
-      <c r="P74" s="23"/>
-      <c r="Q74" s="23"/>
-      <c r="R74" s="23"/>
-      <c r="S74" s="23"/>
-      <c r="T74" s="23"/>
-      <c r="U74" s="24"/>
-      <c r="V74" s="24"/>
-      <c r="W74" s="88"/>
-      <c r="X74" s="88"/>
-      <c r="Y74" s="88"/>
-      <c r="Z74" s="88"/>
-      <c r="AA74" s="89"/>
-      <c r="AB74" s="30"/>
-      <c r="AC74" s="30"/>
-      <c r="AD74" s="21"/>
-    </row>
-    <row r="75" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="21"/>
-      <c r="B75" s="21"/>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="85"/>
-      <c r="F75" s="85"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="21"/>
-      <c r="I75" s="21"/>
-      <c r="J75" s="21"/>
-      <c r="K75" s="23"/>
-      <c r="L75" s="85"/>
-      <c r="M75" s="23"/>
-      <c r="N75" s="86"/>
-      <c r="O75" s="23"/>
-      <c r="P75" s="23"/>
-      <c r="Q75" s="23"/>
-      <c r="R75" s="23"/>
-      <c r="S75" s="23"/>
-      <c r="T75" s="23"/>
-      <c r="U75" s="24"/>
-      <c r="V75" s="24"/>
-      <c r="W75" s="88"/>
-      <c r="X75" s="88"/>
-      <c r="Y75" s="88"/>
-      <c r="Z75" s="88"/>
-      <c r="AA75" s="89"/>
-      <c r="AB75" s="30"/>
-      <c r="AC75" s="30"/>
-      <c r="AD75" s="21"/>
-    </row>
-    <row r="76" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="21"/>
-      <c r="B76" s="21"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="85"/>
-      <c r="F76" s="85"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-      <c r="I76" s="21"/>
-      <c r="J76" s="21"/>
-      <c r="K76" s="23"/>
-      <c r="L76" s="85"/>
-      <c r="M76" s="23"/>
-      <c r="N76" s="86"/>
-      <c r="O76" s="23"/>
-      <c r="P76" s="23"/>
-      <c r="Q76" s="23"/>
-      <c r="R76" s="23"/>
-      <c r="S76" s="23"/>
-      <c r="T76" s="23"/>
-      <c r="U76" s="24"/>
-      <c r="V76" s="24"/>
-      <c r="W76" s="88"/>
-      <c r="X76" s="88"/>
-      <c r="Y76" s="88"/>
-      <c r="Z76" s="88"/>
-      <c r="AA76" s="89"/>
-      <c r="AB76" s="30"/>
-      <c r="AC76" s="30"/>
-      <c r="AD76" s="21"/>
-    </row>
-    <row r="77" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="21"/>
-      <c r="B77" s="21"/>
-      <c r="C77" s="21"/>
-      <c r="D77" s="21"/>
-      <c r="E77" s="85"/>
-      <c r="F77" s="85"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="21"/>
-      <c r="I77" s="21"/>
-      <c r="J77" s="21"/>
-      <c r="K77" s="23"/>
-      <c r="L77" s="85"/>
-      <c r="M77" s="23"/>
-      <c r="N77" s="86"/>
-      <c r="O77" s="23"/>
-      <c r="P77" s="23"/>
-      <c r="Q77" s="23"/>
-      <c r="R77" s="23"/>
-      <c r="S77" s="23"/>
-      <c r="T77" s="23"/>
-      <c r="U77" s="24"/>
-      <c r="V77" s="24"/>
-      <c r="W77" s="88"/>
-      <c r="X77" s="88"/>
-      <c r="Y77" s="88"/>
-      <c r="Z77" s="88"/>
-      <c r="AA77" s="89"/>
-      <c r="AB77" s="30"/>
-      <c r="AC77" s="30"/>
-      <c r="AD77" s="21"/>
-    </row>
-    <row r="78" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="21"/>
-      <c r="B78" s="21"/>
-      <c r="C78" s="21"/>
-      <c r="D78" s="21"/>
-      <c r="E78" s="85"/>
-      <c r="F78" s="85"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="21"/>
-      <c r="I78" s="21"/>
-      <c r="J78" s="21"/>
-      <c r="K78" s="23"/>
-      <c r="L78" s="85"/>
-      <c r="M78" s="23"/>
-      <c r="N78" s="86"/>
-      <c r="O78" s="23"/>
-      <c r="P78" s="23"/>
-      <c r="Q78" s="23"/>
-      <c r="R78" s="23"/>
-      <c r="S78" s="23"/>
-      <c r="T78" s="23"/>
-      <c r="U78" s="24"/>
-      <c r="V78" s="24"/>
-      <c r="W78" s="88"/>
-      <c r="X78" s="88"/>
-      <c r="Y78" s="88"/>
-      <c r="Z78" s="88"/>
-      <c r="AA78" s="89"/>
-      <c r="AB78" s="30"/>
-      <c r="AC78" s="30"/>
-      <c r="AD78" s="21"/>
-    </row>
-    <row r="79" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="21"/>
-      <c r="B79" s="21"/>
-      <c r="C79" s="21"/>
-      <c r="D79" s="21"/>
-      <c r="E79" s="85"/>
-      <c r="F79" s="85"/>
-      <c r="G79" s="21"/>
-      <c r="H79" s="21"/>
-      <c r="I79" s="21"/>
-      <c r="J79" s="21"/>
-      <c r="K79" s="23"/>
-      <c r="L79" s="85"/>
-      <c r="M79" s="23"/>
-      <c r="N79" s="86"/>
-      <c r="O79" s="23"/>
-      <c r="P79" s="23"/>
-      <c r="Q79" s="23"/>
-      <c r="R79" s="23"/>
-      <c r="S79" s="23"/>
-      <c r="T79" s="23"/>
-      <c r="U79" s="24"/>
-      <c r="V79" s="24"/>
-      <c r="W79" s="88"/>
-      <c r="X79" s="88"/>
-      <c r="Y79" s="88"/>
-      <c r="Z79" s="88"/>
-      <c r="AA79" s="89"/>
-      <c r="AB79" s="30"/>
-      <c r="AC79" s="30"/>
-      <c r="AD79" s="21"/>
-    </row>
-    <row r="80" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="21"/>
-      <c r="B80" s="21"/>
-      <c r="C80" s="21"/>
-      <c r="D80" s="21"/>
-      <c r="E80" s="85"/>
-      <c r="F80" s="85"/>
-      <c r="G80" s="21"/>
-      <c r="H80" s="21"/>
-      <c r="I80" s="21"/>
-      <c r="J80" s="21"/>
-      <c r="K80" s="23"/>
-      <c r="L80" s="85"/>
-      <c r="M80" s="23"/>
-      <c r="N80" s="86"/>
-      <c r="O80" s="23"/>
-      <c r="P80" s="23"/>
-      <c r="Q80" s="23"/>
-      <c r="R80" s="23"/>
-      <c r="S80" s="23"/>
-      <c r="T80" s="23"/>
-      <c r="U80" s="24"/>
-      <c r="V80" s="24"/>
-      <c r="W80" s="88"/>
-      <c r="X80" s="88"/>
-      <c r="Y80" s="88"/>
-      <c r="Z80" s="88"/>
-      <c r="AA80" s="89"/>
-      <c r="AB80" s="30"/>
-      <c r="AC80" s="30"/>
-      <c r="AD80" s="21"/>
-    </row>
-    <row r="81" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="21"/>
-      <c r="B81" s="21"/>
-      <c r="C81" s="21"/>
-      <c r="D81" s="21"/>
-      <c r="E81" s="85"/>
-      <c r="F81" s="85"/>
-      <c r="G81" s="21"/>
-      <c r="H81" s="21"/>
-      <c r="I81" s="21"/>
-      <c r="J81" s="21"/>
-      <c r="K81" s="23"/>
-      <c r="L81" s="85"/>
-      <c r="M81" s="23"/>
-      <c r="N81" s="86"/>
-      <c r="O81" s="23"/>
-      <c r="P81" s="23"/>
-      <c r="Q81" s="23"/>
-      <c r="R81" s="23"/>
-      <c r="S81" s="23"/>
-      <c r="T81" s="23"/>
-      <c r="U81" s="24"/>
-      <c r="V81" s="24"/>
-      <c r="W81" s="88"/>
-      <c r="X81" s="88"/>
-      <c r="Y81" s="88"/>
-      <c r="Z81" s="88"/>
-      <c r="AA81" s="89"/>
-      <c r="AB81" s="30"/>
-      <c r="AC81" s="30"/>
-      <c r="AD81" s="21"/>
-    </row>
-    <row r="82" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="21"/>
-      <c r="B82" s="21"/>
-      <c r="C82" s="21"/>
-      <c r="D82" s="21"/>
-      <c r="E82" s="85"/>
-      <c r="F82" s="85"/>
-      <c r="G82" s="21"/>
-      <c r="H82" s="21"/>
-      <c r="I82" s="21"/>
-      <c r="J82" s="21"/>
-      <c r="K82" s="23"/>
-      <c r="L82" s="85"/>
-      <c r="M82" s="23"/>
-      <c r="N82" s="86"/>
-      <c r="O82" s="23"/>
-      <c r="P82" s="23"/>
-      <c r="Q82" s="23"/>
-      <c r="R82" s="23"/>
-      <c r="S82" s="23"/>
-      <c r="T82" s="23"/>
-      <c r="U82" s="24"/>
-      <c r="V82" s="24"/>
-      <c r="W82" s="88"/>
-      <c r="X82" s="88"/>
-      <c r="Y82" s="88"/>
-      <c r="Z82" s="88"/>
-      <c r="AA82" s="89"/>
-      <c r="AB82" s="30"/>
-      <c r="AC82" s="30"/>
-      <c r="AD82" s="21"/>
-    </row>
-    <row r="83" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="21"/>
-      <c r="B83" s="21"/>
-      <c r="C83" s="21"/>
-      <c r="D83" s="21"/>
-      <c r="E83" s="85"/>
-      <c r="F83" s="85"/>
-      <c r="G83" s="21"/>
-      <c r="H83" s="21"/>
-      <c r="I83" s="21"/>
-      <c r="J83" s="21"/>
-      <c r="K83" s="23"/>
-      <c r="L83" s="85"/>
-      <c r="M83" s="23"/>
-      <c r="N83" s="86"/>
-      <c r="O83" s="23"/>
-      <c r="P83" s="23"/>
-      <c r="Q83" s="23"/>
-      <c r="R83" s="23"/>
-      <c r="S83" s="23"/>
-      <c r="T83" s="23"/>
-      <c r="U83" s="24"/>
-      <c r="V83" s="24"/>
-      <c r="W83" s="88"/>
-      <c r="X83" s="88"/>
-      <c r="Y83" s="88"/>
-      <c r="Z83" s="88"/>
-      <c r="AA83" s="89"/>
-      <c r="AB83" s="30"/>
-      <c r="AC83" s="30"/>
-      <c r="AD83" s="21"/>
-    </row>
-    <row r="84" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="21"/>
-      <c r="B84" s="21"/>
-      <c r="C84" s="21"/>
-      <c r="D84" s="21"/>
-      <c r="E84" s="85"/>
-      <c r="F84" s="85"/>
-      <c r="G84" s="21"/>
-      <c r="H84" s="21"/>
-      <c r="I84" s="21"/>
-      <c r="J84" s="21"/>
-      <c r="K84" s="23"/>
-      <c r="L84" s="85"/>
-      <c r="M84" s="23"/>
-      <c r="N84" s="86"/>
-      <c r="O84" s="23"/>
-      <c r="P84" s="23"/>
-      <c r="Q84" s="23"/>
-      <c r="R84" s="23"/>
-      <c r="S84" s="23"/>
-      <c r="T84" s="23"/>
-      <c r="U84" s="24"/>
-      <c r="V84" s="24"/>
-      <c r="W84" s="88"/>
-      <c r="X84" s="88"/>
-      <c r="Y84" s="88"/>
-      <c r="Z84" s="88"/>
-      <c r="AA84" s="89"/>
-      <c r="AB84" s="30"/>
-      <c r="AC84" s="30"/>
-      <c r="AD84" s="21"/>
-    </row>
-    <row r="85" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="21"/>
-      <c r="B85" s="21"/>
-      <c r="C85" s="21"/>
-      <c r="D85" s="21"/>
-      <c r="E85" s="85"/>
-      <c r="F85" s="85"/>
-      <c r="G85" s="21"/>
-      <c r="H85" s="21"/>
-      <c r="I85" s="21"/>
-      <c r="J85" s="21"/>
-      <c r="K85" s="23"/>
-      <c r="L85" s="85"/>
-      <c r="M85" s="23"/>
-      <c r="N85" s="86"/>
-      <c r="O85" s="23"/>
-      <c r="P85" s="23"/>
-      <c r="Q85" s="23"/>
-      <c r="R85" s="23"/>
-      <c r="S85" s="23"/>
-      <c r="T85" s="23"/>
-      <c r="U85" s="24"/>
-      <c r="V85" s="24"/>
-      <c r="W85" s="88"/>
-      <c r="X85" s="88"/>
-      <c r="Y85" s="88"/>
-      <c r="Z85" s="88"/>
-      <c r="AA85" s="89"/>
-      <c r="AB85" s="30"/>
-      <c r="AC85" s="30"/>
-      <c r="AD85" s="21"/>
-    </row>
-    <row r="86" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="21"/>
-      <c r="B86" s="21"/>
-      <c r="C86" s="21"/>
-      <c r="D86" s="21"/>
-      <c r="E86" s="85"/>
-      <c r="F86" s="85"/>
-      <c r="G86" s="21"/>
-      <c r="H86" s="21"/>
-      <c r="I86" s="21"/>
-      <c r="J86" s="21"/>
-      <c r="K86" s="23"/>
-      <c r="L86" s="85"/>
-      <c r="M86" s="23"/>
-      <c r="N86" s="86"/>
-      <c r="O86" s="23"/>
-      <c r="P86" s="23"/>
-      <c r="Q86" s="23"/>
-      <c r="R86" s="23"/>
-      <c r="S86" s="23"/>
-      <c r="T86" s="23"/>
-      <c r="U86" s="24"/>
-      <c r="V86" s="24"/>
-      <c r="W86" s="88"/>
-      <c r="X86" s="88"/>
-      <c r="Y86" s="88"/>
-      <c r="Z86" s="88"/>
-      <c r="AA86" s="89"/>
-      <c r="AB86" s="30"/>
-      <c r="AC86" s="30"/>
-      <c r="AD86" s="21"/>
-    </row>
-    <row r="87" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="21"/>
-      <c r="B87" s="21"/>
-      <c r="C87" s="21"/>
-      <c r="D87" s="21"/>
-      <c r="E87" s="85"/>
-      <c r="F87" s="85"/>
-      <c r="G87" s="21"/>
-      <c r="H87" s="21"/>
-      <c r="I87" s="21"/>
-      <c r="J87" s="21"/>
-      <c r="K87" s="23"/>
-      <c r="L87" s="85"/>
-      <c r="M87" s="23"/>
-      <c r="N87" s="86"/>
-      <c r="O87" s="23"/>
-      <c r="P87" s="23"/>
-      <c r="Q87" s="23"/>
-      <c r="R87" s="23"/>
-      <c r="S87" s="23"/>
-      <c r="T87" s="23"/>
-      <c r="U87" s="24"/>
-      <c r="V87" s="24"/>
-      <c r="W87" s="88"/>
-      <c r="X87" s="88"/>
-      <c r="Y87" s="88"/>
-      <c r="Z87" s="88"/>
-      <c r="AA87" s="89"/>
-      <c r="AB87" s="30"/>
-      <c r="AC87" s="30"/>
-      <c r="AD87" s="21"/>
-    </row>
-    <row r="88" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="21"/>
-      <c r="B88" s="21"/>
-      <c r="C88" s="21"/>
-      <c r="D88" s="21"/>
-      <c r="E88" s="85"/>
-      <c r="F88" s="85"/>
-      <c r="G88" s="21"/>
-      <c r="H88" s="21"/>
-      <c r="I88" s="21"/>
-      <c r="J88" s="21"/>
-      <c r="K88" s="23"/>
-      <c r="L88" s="85"/>
-      <c r="M88" s="23"/>
-      <c r="N88" s="86"/>
-      <c r="O88" s="23"/>
-      <c r="P88" s="23"/>
-      <c r="Q88" s="23"/>
-      <c r="R88" s="23"/>
-      <c r="S88" s="23"/>
-      <c r="T88" s="23"/>
-      <c r="U88" s="24"/>
-      <c r="V88" s="24"/>
-      <c r="W88" s="88"/>
-      <c r="X88" s="88"/>
-      <c r="Y88" s="88"/>
-      <c r="Z88" s="88"/>
-      <c r="AA88" s="89"/>
-      <c r="AB88" s="30"/>
-      <c r="AC88" s="30"/>
-      <c r="AD88" s="21"/>
-    </row>
-    <row r="89" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="21"/>
-      <c r="B89" s="21"/>
-      <c r="C89" s="21"/>
-      <c r="D89" s="21"/>
-      <c r="E89" s="85"/>
-      <c r="F89" s="85"/>
-      <c r="G89" s="21"/>
-      <c r="H89" s="21"/>
-      <c r="I89" s="21"/>
-      <c r="J89" s="21"/>
-      <c r="K89" s="23"/>
-      <c r="L89" s="85"/>
-      <c r="M89" s="23"/>
-      <c r="N89" s="86"/>
-      <c r="O89" s="23"/>
-      <c r="P89" s="23"/>
-      <c r="Q89" s="23"/>
-      <c r="R89" s="23"/>
-      <c r="S89" s="23"/>
-      <c r="T89" s="23"/>
-      <c r="U89" s="24"/>
-      <c r="V89" s="24"/>
-      <c r="W89" s="88"/>
-      <c r="X89" s="88"/>
-      <c r="Y89" s="88"/>
-      <c r="Z89" s="88"/>
-      <c r="AA89" s="89"/>
-      <c r="AB89" s="30"/>
-      <c r="AC89" s="30"/>
-      <c r="AD89" s="21"/>
-    </row>
-    <row r="90" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="21"/>
-      <c r="B90" s="21"/>
-      <c r="C90" s="21"/>
-      <c r="D90" s="21"/>
-      <c r="E90" s="85"/>
-      <c r="F90" s="85"/>
-      <c r="G90" s="21"/>
-      <c r="H90" s="21"/>
-      <c r="I90" s="21"/>
-      <c r="J90" s="21"/>
-      <c r="K90" s="23"/>
-      <c r="L90" s="85"/>
-      <c r="M90" s="23"/>
-      <c r="N90" s="86"/>
-      <c r="O90" s="23"/>
-      <c r="P90" s="23"/>
-      <c r="Q90" s="23"/>
-      <c r="R90" s="23"/>
-      <c r="S90" s="23"/>
-      <c r="T90" s="23"/>
-      <c r="U90" s="24"/>
-      <c r="V90" s="24"/>
-      <c r="W90" s="88"/>
-      <c r="X90" s="88"/>
-      <c r="Y90" s="88"/>
-      <c r="Z90" s="88"/>
-      <c r="AA90" s="89"/>
-      <c r="AB90" s="30"/>
-      <c r="AC90" s="30"/>
-      <c r="AD90" s="21"/>
-    </row>
-    <row r="91" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="21"/>
-      <c r="B91" s="21"/>
-      <c r="C91" s="21"/>
-      <c r="D91" s="21"/>
-      <c r="E91" s="85"/>
-      <c r="F91" s="85"/>
-      <c r="G91" s="21"/>
-      <c r="H91" s="21"/>
-      <c r="I91" s="21"/>
-      <c r="J91" s="21"/>
-      <c r="K91" s="23"/>
-      <c r="L91" s="85"/>
-      <c r="M91" s="23"/>
-      <c r="N91" s="86"/>
-      <c r="O91" s="23"/>
-      <c r="P91" s="23"/>
-      <c r="Q91" s="23"/>
-      <c r="R91" s="23"/>
-      <c r="S91" s="23"/>
-      <c r="T91" s="23"/>
-      <c r="U91" s="24"/>
-      <c r="V91" s="24"/>
-      <c r="W91" s="88"/>
-      <c r="X91" s="88"/>
-      <c r="Y91" s="88"/>
-      <c r="Z91" s="88"/>
-      <c r="AA91" s="89"/>
-      <c r="AB91" s="30"/>
-      <c r="AC91" s="30"/>
-      <c r="AD91" s="21"/>
-    </row>
-    <row r="92" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="21"/>
-      <c r="B92" s="21"/>
-      <c r="C92" s="21"/>
-      <c r="D92" s="21"/>
-      <c r="E92" s="85"/>
-      <c r="F92" s="85"/>
-      <c r="G92" s="21"/>
-      <c r="H92" s="21"/>
-      <c r="I92" s="21"/>
-      <c r="J92" s="21"/>
-      <c r="K92" s="23"/>
-      <c r="L92" s="85"/>
-      <c r="M92" s="23"/>
-      <c r="N92" s="86"/>
-      <c r="O92" s="23"/>
-      <c r="P92" s="23"/>
-      <c r="Q92" s="23"/>
-      <c r="R92" s="23"/>
-      <c r="S92" s="23"/>
-      <c r="T92" s="23"/>
-      <c r="U92" s="24"/>
-      <c r="V92" s="24"/>
-      <c r="W92" s="88"/>
-      <c r="X92" s="88"/>
-      <c r="Y92" s="88"/>
-      <c r="Z92" s="88"/>
-      <c r="AA92" s="89"/>
-      <c r="AB92" s="30"/>
-      <c r="AC92" s="30"/>
-      <c r="AD92" s="21"/>
-    </row>
-    <row r="93" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="21"/>
-      <c r="B93" s="21"/>
-      <c r="C93" s="21"/>
-      <c r="D93" s="21"/>
-      <c r="E93" s="85"/>
-      <c r="F93" s="85"/>
-      <c r="G93" s="21"/>
-      <c r="H93" s="21"/>
-      <c r="I93" s="21"/>
-      <c r="J93" s="21"/>
-      <c r="K93" s="23"/>
-      <c r="L93" s="85"/>
-      <c r="M93" s="23"/>
-      <c r="N93" s="86"/>
-      <c r="O93" s="23"/>
-      <c r="P93" s="23"/>
-      <c r="Q93" s="23"/>
-      <c r="R93" s="23"/>
-      <c r="S93" s="23"/>
-      <c r="T93" s="23"/>
-      <c r="U93" s="24"/>
-      <c r="V93" s="24"/>
-      <c r="W93" s="88"/>
-      <c r="X93" s="88"/>
-      <c r="Y93" s="88"/>
-      <c r="Z93" s="88"/>
-      <c r="AA93" s="89"/>
-      <c r="AB93" s="30"/>
-      <c r="AC93" s="30"/>
-      <c r="AD93" s="21"/>
-    </row>
-    <row r="94" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="21"/>
-      <c r="B94" s="21"/>
-      <c r="C94" s="21"/>
-      <c r="D94" s="21"/>
-      <c r="E94" s="85"/>
-      <c r="F94" s="85"/>
-      <c r="G94" s="21"/>
-      <c r="H94" s="21"/>
-      <c r="I94" s="21"/>
-      <c r="J94" s="21"/>
-      <c r="K94" s="23"/>
-      <c r="L94" s="85"/>
-      <c r="M94" s="23"/>
-      <c r="N94" s="86"/>
-      <c r="O94" s="23"/>
-      <c r="P94" s="23"/>
-      <c r="Q94" s="23"/>
-      <c r="R94" s="23"/>
-      <c r="S94" s="23"/>
-      <c r="T94" s="23"/>
-      <c r="U94" s="24"/>
-      <c r="V94" s="24"/>
-      <c r="W94" s="88"/>
-      <c r="X94" s="88"/>
-      <c r="Y94" s="88"/>
-      <c r="Z94" s="88"/>
-      <c r="AA94" s="89"/>
-      <c r="AB94" s="30"/>
-      <c r="AC94" s="30"/>
-      <c r="AD94" s="21"/>
-    </row>
-    <row r="95" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="21"/>
-      <c r="B95" s="21"/>
-      <c r="C95" s="21"/>
-      <c r="D95" s="21"/>
-      <c r="E95" s="85"/>
-      <c r="F95" s="85"/>
-      <c r="G95" s="21"/>
-      <c r="H95" s="21"/>
-      <c r="I95" s="21"/>
-      <c r="J95" s="21"/>
-      <c r="K95" s="23"/>
-      <c r="L95" s="85"/>
-      <c r="M95" s="23"/>
-      <c r="N95" s="86"/>
-      <c r="O95" s="23"/>
-      <c r="P95" s="23"/>
-      <c r="Q95" s="23"/>
-      <c r="R95" s="23"/>
-      <c r="S95" s="23"/>
-      <c r="T95" s="23"/>
-      <c r="U95" s="24"/>
-      <c r="V95" s="24"/>
-      <c r="W95" s="88"/>
-      <c r="X95" s="88"/>
-      <c r="Y95" s="88"/>
-      <c r="Z95" s="88"/>
-      <c r="AA95" s="89"/>
-      <c r="AB95" s="30"/>
-      <c r="AC95" s="30"/>
-      <c r="AD95" s="21"/>
-    </row>
-    <row r="96" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="21"/>
-      <c r="B96" s="21"/>
-      <c r="C96" s="21"/>
-      <c r="D96" s="21"/>
-      <c r="E96" s="85"/>
-      <c r="F96" s="85"/>
-      <c r="G96" s="21"/>
-      <c r="H96" s="21"/>
-      <c r="I96" s="21"/>
-      <c r="J96" s="21"/>
-      <c r="K96" s="23"/>
-      <c r="L96" s="85"/>
-      <c r="M96" s="23"/>
-      <c r="N96" s="86"/>
-      <c r="O96" s="23"/>
-      <c r="P96" s="23"/>
-      <c r="Q96" s="23"/>
-      <c r="R96" s="23"/>
-      <c r="S96" s="23"/>
-      <c r="T96" s="23"/>
-      <c r="U96" s="24"/>
-      <c r="V96" s="24"/>
-      <c r="W96" s="88"/>
-      <c r="X96" s="88"/>
-      <c r="Y96" s="88"/>
-      <c r="Z96" s="88"/>
-      <c r="AA96" s="89"/>
-      <c r="AB96" s="30"/>
-      <c r="AC96" s="30"/>
-      <c r="AD96" s="21"/>
-    </row>
-    <row r="97" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="21"/>
-      <c r="B97" s="21"/>
-      <c r="C97" s="21"/>
-      <c r="D97" s="21"/>
-      <c r="E97" s="85"/>
-      <c r="F97" s="85"/>
-      <c r="G97" s="21"/>
-      <c r="H97" s="21"/>
-      <c r="I97" s="21"/>
-      <c r="J97" s="21"/>
-      <c r="K97" s="23"/>
-      <c r="L97" s="85"/>
-      <c r="M97" s="23"/>
-      <c r="N97" s="86"/>
-      <c r="O97" s="23"/>
-      <c r="P97" s="23"/>
-      <c r="Q97" s="23"/>
-      <c r="R97" s="23"/>
-      <c r="S97" s="23"/>
-      <c r="T97" s="23"/>
-      <c r="U97" s="24"/>
-      <c r="V97" s="24"/>
-      <c r="W97" s="88"/>
-      <c r="X97" s="88"/>
-      <c r="Y97" s="88"/>
-      <c r="Z97" s="88"/>
-      <c r="AA97" s="89"/>
-      <c r="AB97" s="30"/>
-      <c r="AC97" s="30"/>
-      <c r="AD97" s="21"/>
-    </row>
-    <row r="98" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="21"/>
-      <c r="B98" s="21"/>
-      <c r="C98" s="21"/>
-      <c r="D98" s="21"/>
-      <c r="E98" s="85"/>
-      <c r="F98" s="85"/>
-      <c r="G98" s="21"/>
-      <c r="H98" s="21"/>
-      <c r="I98" s="21"/>
-      <c r="J98" s="21"/>
-      <c r="K98" s="23"/>
-      <c r="L98" s="85"/>
-      <c r="M98" s="23"/>
-      <c r="N98" s="86"/>
-      <c r="O98" s="23"/>
-      <c r="P98" s="23"/>
-      <c r="Q98" s="23"/>
-      <c r="R98" s="23"/>
-      <c r="S98" s="23"/>
-      <c r="T98" s="23"/>
-      <c r="U98" s="24"/>
-      <c r="V98" s="24"/>
-      <c r="W98" s="88"/>
-      <c r="X98" s="88"/>
-      <c r="Y98" s="88"/>
-      <c r="Z98" s="88"/>
-      <c r="AA98" s="89"/>
-      <c r="AB98" s="30"/>
-      <c r="AC98" s="30"/>
-      <c r="AD98" s="21"/>
-    </row>
-    <row r="99" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="21"/>
-      <c r="B99" s="21"/>
-      <c r="C99" s="21"/>
-      <c r="D99" s="21"/>
-      <c r="E99" s="85"/>
-      <c r="F99" s="85"/>
-      <c r="G99" s="21"/>
-      <c r="H99" s="21"/>
-      <c r="I99" s="21"/>
-      <c r="J99" s="21"/>
-      <c r="K99" s="23"/>
-      <c r="L99" s="85"/>
-      <c r="M99" s="23"/>
-      <c r="N99" s="86"/>
-      <c r="O99" s="23"/>
-      <c r="P99" s="23"/>
-      <c r="Q99" s="23"/>
-      <c r="R99" s="23"/>
-      <c r="S99" s="23"/>
-      <c r="T99" s="23"/>
-      <c r="U99" s="24"/>
-      <c r="V99" s="24"/>
-      <c r="W99" s="88"/>
-      <c r="X99" s="88"/>
-      <c r="Y99" s="88"/>
-      <c r="Z99" s="88"/>
-      <c r="AA99" s="89"/>
-      <c r="AB99" s="30"/>
-      <c r="AC99" s="30"/>
-      <c r="AD99" s="21"/>
-    </row>
-    <row r="100" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="21"/>
-      <c r="B100" s="21"/>
-      <c r="C100" s="21"/>
-      <c r="D100" s="21"/>
-      <c r="E100" s="85"/>
-      <c r="F100" s="85"/>
-      <c r="G100" s="21"/>
-      <c r="H100" s="21"/>
-      <c r="I100" s="21"/>
-      <c r="J100" s="21"/>
-      <c r="K100" s="23"/>
-      <c r="L100" s="85"/>
-      <c r="M100" s="23"/>
-      <c r="N100" s="86"/>
-      <c r="O100" s="23"/>
-      <c r="P100" s="23"/>
-      <c r="Q100" s="23"/>
-      <c r="R100" s="23"/>
-      <c r="S100" s="23"/>
-      <c r="T100" s="23"/>
-      <c r="U100" s="24"/>
-      <c r="V100" s="24"/>
-      <c r="W100" s="88"/>
-      <c r="X100" s="88"/>
-      <c r="Y100" s="88"/>
-      <c r="Z100" s="88"/>
-      <c r="AA100" s="89"/>
-      <c r="AB100" s="30"/>
-      <c r="AC100" s="30"/>
-      <c r="AD100" s="21"/>
-    </row>
-    <row r="101" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="21"/>
-      <c r="B101" s="21"/>
-      <c r="C101" s="21"/>
-      <c r="D101" s="21"/>
-      <c r="E101" s="85"/>
-      <c r="F101" s="85"/>
-      <c r="G101" s="21"/>
-      <c r="H101" s="21"/>
-      <c r="I101" s="21"/>
-      <c r="J101" s="21"/>
-      <c r="K101" s="23"/>
-      <c r="L101" s="85"/>
-      <c r="M101" s="23"/>
-      <c r="N101" s="86"/>
-      <c r="O101" s="23"/>
-      <c r="P101" s="23"/>
-      <c r="Q101" s="23"/>
-      <c r="R101" s="23"/>
-      <c r="S101" s="23"/>
-      <c r="T101" s="23"/>
-      <c r="U101" s="24"/>
-      <c r="V101" s="24"/>
-      <c r="W101" s="88"/>
-      <c r="X101" s="88"/>
-      <c r="Y101" s="88"/>
-      <c r="Z101" s="88"/>
-      <c r="AA101" s="89"/>
-      <c r="AB101" s="30"/>
-      <c r="AC101" s="30"/>
-      <c r="AD101" s="21"/>
-    </row>
-    <row r="102" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="21"/>
-      <c r="B102" s="21"/>
-      <c r="C102" s="21"/>
-      <c r="D102" s="21"/>
-      <c r="E102" s="85"/>
-      <c r="F102" s="85"/>
-      <c r="G102" s="21"/>
-      <c r="H102" s="21"/>
-      <c r="I102" s="21"/>
-      <c r="J102" s="21"/>
-      <c r="K102" s="23"/>
-      <c r="L102" s="85"/>
-      <c r="M102" s="23"/>
-      <c r="N102" s="86"/>
-      <c r="O102" s="23"/>
-      <c r="P102" s="23"/>
-      <c r="Q102" s="23"/>
-      <c r="R102" s="23"/>
-      <c r="S102" s="23"/>
-      <c r="T102" s="23"/>
-      <c r="U102" s="24"/>
-      <c r="V102" s="24"/>
-      <c r="W102" s="88"/>
-      <c r="X102" s="88"/>
-      <c r="Y102" s="88"/>
-      <c r="Z102" s="88"/>
-      <c r="AA102" s="89"/>
-      <c r="AB102" s="30"/>
-      <c r="AC102" s="30"/>
-      <c r="AD102" s="21"/>
-    </row>
-    <row r="103" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="21"/>
-      <c r="B103" s="21"/>
-      <c r="C103" s="21"/>
-      <c r="D103" s="21"/>
-      <c r="E103" s="85"/>
-      <c r="F103" s="85"/>
-      <c r="G103" s="21"/>
-      <c r="H103" s="21"/>
-      <c r="I103" s="21"/>
-      <c r="J103" s="21"/>
-      <c r="K103" s="23"/>
-      <c r="L103" s="85"/>
-      <c r="M103" s="23"/>
-      <c r="N103" s="86"/>
-      <c r="O103" s="23"/>
-      <c r="P103" s="23"/>
-      <c r="Q103" s="23"/>
-      <c r="R103" s="23"/>
-      <c r="S103" s="23"/>
-      <c r="T103" s="23"/>
-      <c r="U103" s="24"/>
-      <c r="V103" s="24"/>
-      <c r="W103" s="88"/>
-      <c r="X103" s="88"/>
-      <c r="Y103" s="88"/>
-      <c r="Z103" s="88"/>
-      <c r="AA103" s="89"/>
-      <c r="AB103" s="30"/>
-      <c r="AC103" s="30"/>
-      <c r="AD103" s="21"/>
-    </row>
-    <row r="104" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="21"/>
-      <c r="B104" s="21"/>
-      <c r="C104" s="21"/>
-      <c r="D104" s="21"/>
-      <c r="E104" s="85"/>
-      <c r="F104" s="85"/>
-      <c r="G104" s="21"/>
-      <c r="H104" s="21"/>
-      <c r="I104" s="21"/>
-      <c r="J104" s="21"/>
-      <c r="K104" s="23"/>
-      <c r="L104" s="85"/>
-      <c r="M104" s="23"/>
-      <c r="N104" s="86"/>
-      <c r="O104" s="23"/>
-      <c r="P104" s="23"/>
-      <c r="Q104" s="23"/>
-      <c r="R104" s="23"/>
-      <c r="S104" s="23"/>
-      <c r="T104" s="23"/>
-      <c r="U104" s="24"/>
-      <c r="V104" s="24"/>
-      <c r="W104" s="88"/>
-      <c r="X104" s="88"/>
-      <c r="Y104" s="88"/>
-      <c r="Z104" s="88"/>
-      <c r="AA104" s="89"/>
-      <c r="AB104" s="30"/>
-      <c r="AC104" s="30"/>
-      <c r="AD104" s="21"/>
-    </row>
-    <row r="105" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="21"/>
-      <c r="B105" s="21"/>
-      <c r="C105" s="21"/>
-      <c r="D105" s="21"/>
-      <c r="E105" s="85"/>
-      <c r="F105" s="85"/>
-      <c r="G105" s="21"/>
-      <c r="H105" s="21"/>
-      <c r="I105" s="21"/>
-      <c r="J105" s="21"/>
-      <c r="K105" s="23"/>
-      <c r="L105" s="85"/>
-      <c r="M105" s="23"/>
-      <c r="N105" s="86"/>
-      <c r="O105" s="23"/>
-      <c r="P105" s="23"/>
-      <c r="Q105" s="23"/>
-      <c r="R105" s="23"/>
-      <c r="S105" s="23"/>
-      <c r="T105" s="23"/>
-      <c r="U105" s="24"/>
-      <c r="V105" s="24"/>
-      <c r="W105" s="88"/>
-      <c r="X105" s="88"/>
-      <c r="Y105" s="88"/>
-      <c r="Z105" s="88"/>
-      <c r="AA105" s="89"/>
-      <c r="AB105" s="30"/>
-      <c r="AC105" s="30"/>
-      <c r="AD105" s="21"/>
-    </row>
-    <row r="106" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="21"/>
-      <c r="B106" s="21"/>
-      <c r="C106" s="21"/>
-      <c r="D106" s="21"/>
-      <c r="E106" s="85"/>
-      <c r="F106" s="85"/>
-      <c r="G106" s="21"/>
-      <c r="H106" s="21"/>
-      <c r="I106" s="21"/>
-      <c r="J106" s="21"/>
-      <c r="K106" s="23"/>
-      <c r="L106" s="85"/>
-      <c r="M106" s="23"/>
-      <c r="N106" s="86"/>
-      <c r="O106" s="23"/>
-      <c r="P106" s="23"/>
-      <c r="Q106" s="23"/>
-      <c r="R106" s="23"/>
-      <c r="S106" s="23"/>
-      <c r="T106" s="23"/>
-      <c r="U106" s="24"/>
-      <c r="V106" s="24"/>
-      <c r="W106" s="88"/>
-      <c r="X106" s="88"/>
-      <c r="Y106" s="88"/>
-      <c r="Z106" s="88"/>
-      <c r="AA106" s="89"/>
-      <c r="AB106" s="30"/>
-      <c r="AC106" s="30"/>
-      <c r="AD106" s="21"/>
-    </row>
-    <row r="107" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="21"/>
-      <c r="B107" s="21"/>
-      <c r="C107" s="21"/>
-      <c r="D107" s="21"/>
-      <c r="E107" s="85"/>
-      <c r="F107" s="85"/>
-      <c r="G107" s="21"/>
-      <c r="H107" s="21"/>
-      <c r="I107" s="21"/>
-      <c r="J107" s="21"/>
-      <c r="K107" s="23"/>
-      <c r="L107" s="85"/>
-      <c r="M107" s="23"/>
-      <c r="N107" s="86"/>
-      <c r="O107" s="23"/>
-      <c r="P107" s="23"/>
-      <c r="Q107" s="23"/>
-      <c r="R107" s="23"/>
-      <c r="S107" s="23"/>
-      <c r="T107" s="23"/>
-      <c r="U107" s="24"/>
-      <c r="V107" s="24"/>
-      <c r="W107" s="88"/>
-      <c r="X107" s="88"/>
-      <c r="Y107" s="88"/>
-      <c r="Z107" s="88"/>
-      <c r="AA107" s="89"/>
-      <c r="AB107" s="30"/>
-      <c r="AC107" s="30"/>
-      <c r="AD107" s="21"/>
-    </row>
-    <row r="108" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="21"/>
-      <c r="B108" s="21"/>
-      <c r="C108" s="21"/>
-      <c r="D108" s="21"/>
-      <c r="E108" s="85"/>
-      <c r="F108" s="85"/>
-      <c r="G108" s="21"/>
-      <c r="H108" s="21"/>
-      <c r="I108" s="21"/>
-      <c r="J108" s="21"/>
-      <c r="K108" s="23"/>
-      <c r="L108" s="85"/>
-      <c r="M108" s="23"/>
-      <c r="N108" s="86"/>
-      <c r="O108" s="23"/>
-      <c r="P108" s="23"/>
-      <c r="Q108" s="23"/>
-      <c r="R108" s="23"/>
-      <c r="S108" s="23"/>
-      <c r="T108" s="23"/>
-      <c r="U108" s="24"/>
-      <c r="V108" s="24"/>
-      <c r="W108" s="88"/>
-      <c r="X108" s="88"/>
-      <c r="Y108" s="88"/>
-      <c r="Z108" s="88"/>
-      <c r="AA108" s="89"/>
-      <c r="AB108" s="30"/>
-      <c r="AC108" s="30"/>
-      <c r="AD108" s="21"/>
-    </row>
-    <row r="109" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="21"/>
-      <c r="B109" s="21"/>
-      <c r="C109" s="21"/>
-      <c r="D109" s="21"/>
-      <c r="E109" s="85"/>
-      <c r="F109" s="85"/>
-      <c r="G109" s="21"/>
-      <c r="H109" s="21"/>
-      <c r="I109" s="21"/>
-      <c r="J109" s="21"/>
-      <c r="K109" s="23"/>
-      <c r="L109" s="85"/>
-      <c r="M109" s="23"/>
-      <c r="N109" s="86"/>
-      <c r="O109" s="23"/>
-      <c r="P109" s="23"/>
-      <c r="Q109" s="23"/>
-      <c r="R109" s="23"/>
-      <c r="S109" s="23"/>
-      <c r="T109" s="23"/>
-      <c r="U109" s="24"/>
-      <c r="V109" s="24"/>
-      <c r="W109" s="88"/>
-      <c r="X109" s="88"/>
-      <c r="Y109" s="88"/>
-      <c r="Z109" s="88"/>
-      <c r="AA109" s="89"/>
-      <c r="AB109" s="30"/>
-      <c r="AC109" s="30"/>
-      <c r="AD109" s="21"/>
-    </row>
-    <row r="110" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="21"/>
-      <c r="B110" s="21"/>
-      <c r="C110" s="21"/>
-      <c r="D110" s="21"/>
-      <c r="E110" s="85"/>
-      <c r="F110" s="85"/>
-      <c r="G110" s="21"/>
-      <c r="H110" s="21"/>
-      <c r="I110" s="21"/>
-      <c r="J110" s="21"/>
-      <c r="K110" s="23"/>
-      <c r="L110" s="85"/>
-      <c r="M110" s="23"/>
-      <c r="N110" s="86"/>
-      <c r="O110" s="23"/>
-      <c r="P110" s="23"/>
-      <c r="Q110" s="23"/>
-      <c r="R110" s="23"/>
-      <c r="S110" s="23"/>
-      <c r="T110" s="23"/>
-      <c r="U110" s="24"/>
-      <c r="V110" s="24"/>
-      <c r="W110" s="88"/>
-      <c r="X110" s="88"/>
-      <c r="Y110" s="88"/>
-      <c r="Z110" s="88"/>
-      <c r="AA110" s="89"/>
-      <c r="AB110" s="30"/>
-      <c r="AC110" s="30"/>
-      <c r="AD110" s="21"/>
-    </row>
-    <row r="111" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="21"/>
-      <c r="B111" s="21"/>
-      <c r="C111" s="21"/>
-      <c r="D111" s="21"/>
-      <c r="E111" s="85"/>
-      <c r="F111" s="85"/>
-      <c r="G111" s="21"/>
-      <c r="H111" s="21"/>
-      <c r="I111" s="21"/>
-      <c r="J111" s="21"/>
-      <c r="K111" s="23"/>
-      <c r="L111" s="85"/>
-      <c r="M111" s="23"/>
-      <c r="N111" s="86"/>
-      <c r="O111" s="23"/>
-      <c r="P111" s="23"/>
-      <c r="Q111" s="23"/>
-      <c r="R111" s="23"/>
-      <c r="S111" s="23"/>
-      <c r="T111" s="23"/>
-      <c r="U111" s="24"/>
-      <c r="V111" s="24"/>
-      <c r="W111" s="88"/>
-      <c r="X111" s="88"/>
-      <c r="Y111" s="88"/>
-      <c r="Z111" s="88"/>
-      <c r="AA111" s="89"/>
-      <c r="AB111" s="30"/>
-      <c r="AC111" s="30"/>
-      <c r="AD111" s="21"/>
-    </row>
-    <row r="112" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="21"/>
-      <c r="B112" s="21"/>
-      <c r="C112" s="21"/>
-      <c r="D112" s="21"/>
-      <c r="E112" s="85"/>
-      <c r="F112" s="85"/>
-      <c r="G112" s="21"/>
-      <c r="H112" s="21"/>
-      <c r="I112" s="21"/>
-      <c r="J112" s="21"/>
-      <c r="K112" s="23"/>
-      <c r="L112" s="85"/>
-      <c r="M112" s="23"/>
-      <c r="N112" s="86"/>
-      <c r="O112" s="23"/>
-      <c r="P112" s="23"/>
-      <c r="Q112" s="23"/>
-      <c r="R112" s="23"/>
-      <c r="S112" s="23"/>
-      <c r="T112" s="23"/>
-      <c r="U112" s="24"/>
-      <c r="V112" s="24"/>
-      <c r="W112" s="88"/>
-      <c r="X112" s="88"/>
-      <c r="Y112" s="88"/>
-      <c r="Z112" s="88"/>
-      <c r="AA112" s="89"/>
-      <c r="AB112" s="30"/>
-      <c r="AC112" s="30"/>
-      <c r="AD112" s="21"/>
-    </row>
-    <row r="113" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="21"/>
-      <c r="B113" s="21"/>
-      <c r="C113" s="21"/>
-      <c r="D113" s="21"/>
-      <c r="E113" s="85"/>
-      <c r="F113" s="85"/>
-      <c r="G113" s="21"/>
-      <c r="H113" s="21"/>
-      <c r="I113" s="21"/>
-      <c r="J113" s="21"/>
-      <c r="K113" s="23"/>
-      <c r="L113" s="85"/>
-      <c r="M113" s="23"/>
-      <c r="N113" s="86"/>
-      <c r="O113" s="23"/>
-      <c r="P113" s="23"/>
-      <c r="Q113" s="23"/>
-      <c r="R113" s="23"/>
-      <c r="S113" s="23"/>
-      <c r="T113" s="23"/>
-      <c r="U113" s="24"/>
-      <c r="V113" s="24"/>
-      <c r="W113" s="88"/>
-      <c r="X113" s="88"/>
-      <c r="Y113" s="88"/>
-      <c r="Z113" s="88"/>
-      <c r="AA113" s="89"/>
-      <c r="AB113" s="30"/>
-      <c r="AC113" s="30"/>
-      <c r="AD113" s="21"/>
-    </row>
-    <row r="114" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="21"/>
-      <c r="B114" s="21"/>
-      <c r="C114" s="21"/>
-      <c r="D114" s="21"/>
-      <c r="E114" s="85"/>
-      <c r="F114" s="85"/>
-      <c r="G114" s="21"/>
-      <c r="H114" s="21"/>
-      <c r="I114" s="21"/>
-      <c r="J114" s="21"/>
-      <c r="K114" s="23"/>
-      <c r="L114" s="85"/>
-      <c r="M114" s="23"/>
-      <c r="N114" s="86"/>
-      <c r="O114" s="23"/>
-      <c r="P114" s="23"/>
-      <c r="Q114" s="23"/>
-      <c r="R114" s="23"/>
-      <c r="S114" s="23"/>
-      <c r="T114" s="23"/>
-      <c r="U114" s="24"/>
-      <c r="V114" s="24"/>
-      <c r="W114" s="88"/>
-      <c r="X114" s="88"/>
-      <c r="Y114" s="88"/>
-      <c r="Z114" s="88"/>
-      <c r="AA114" s="89"/>
-      <c r="AB114" s="30"/>
-      <c r="AC114" s="30"/>
-      <c r="AD114" s="21"/>
-    </row>
-    <row r="115" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="21"/>
-      <c r="B115" s="21"/>
-      <c r="C115" s="21"/>
-      <c r="D115" s="21"/>
-      <c r="E115" s="85"/>
-      <c r="F115" s="85"/>
-      <c r="G115" s="21"/>
-      <c r="H115" s="21"/>
-      <c r="I115" s="21"/>
-      <c r="J115" s="21"/>
-      <c r="K115" s="23"/>
-      <c r="L115" s="85"/>
-      <c r="M115" s="23"/>
-      <c r="N115" s="86"/>
-      <c r="O115" s="23"/>
-      <c r="P115" s="23"/>
-      <c r="Q115" s="23"/>
-      <c r="R115" s="23"/>
-      <c r="S115" s="23"/>
-      <c r="T115" s="23"/>
-      <c r="U115" s="24"/>
-      <c r="V115" s="24"/>
-      <c r="W115" s="88"/>
-      <c r="X115" s="88"/>
-      <c r="Y115" s="88"/>
-      <c r="Z115" s="88"/>
-      <c r="AA115" s="89"/>
-      <c r="AB115" s="30"/>
-      <c r="AC115" s="30"/>
-      <c r="AD115" s="21"/>
-    </row>
-    <row r="116" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="21"/>
-      <c r="B116" s="21"/>
-      <c r="C116" s="21"/>
-      <c r="D116" s="21"/>
-      <c r="E116" s="85"/>
-      <c r="F116" s="85"/>
-      <c r="G116" s="21"/>
-      <c r="H116" s="21"/>
-      <c r="I116" s="21"/>
-      <c r="J116" s="21"/>
-      <c r="K116" s="23"/>
-      <c r="L116" s="85"/>
-      <c r="M116" s="23"/>
-      <c r="N116" s="86"/>
-      <c r="O116" s="23"/>
-      <c r="P116" s="23"/>
-      <c r="Q116" s="23"/>
-      <c r="R116" s="23"/>
-      <c r="S116" s="23"/>
-      <c r="T116" s="23"/>
-      <c r="U116" s="24"/>
-      <c r="V116" s="24"/>
-      <c r="W116" s="88"/>
-      <c r="X116" s="88"/>
-      <c r="Y116" s="88"/>
-      <c r="Z116" s="88"/>
-      <c r="AA116" s="89"/>
-      <c r="AB116" s="30"/>
-      <c r="AC116" s="30"/>
-      <c r="AD116" s="21"/>
-    </row>
-    <row r="117" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="21"/>
-      <c r="B117" s="21"/>
-      <c r="C117" s="21"/>
-      <c r="D117" s="21"/>
-      <c r="E117" s="85"/>
-      <c r="F117" s="85"/>
-      <c r="G117" s="21"/>
-      <c r="H117" s="21"/>
-      <c r="I117" s="21"/>
-      <c r="J117" s="21"/>
-      <c r="K117" s="23"/>
-      <c r="L117" s="85"/>
-      <c r="M117" s="23"/>
-      <c r="N117" s="86"/>
-      <c r="O117" s="23"/>
-      <c r="P117" s="23"/>
-      <c r="Q117" s="23"/>
-      <c r="R117" s="23"/>
-      <c r="S117" s="23"/>
-      <c r="T117" s="23"/>
-      <c r="U117" s="24"/>
-      <c r="V117" s="24"/>
-      <c r="W117" s="88"/>
-      <c r="X117" s="88"/>
-      <c r="Y117" s="88"/>
-      <c r="Z117" s="88"/>
-      <c r="AA117" s="89"/>
-      <c r="AB117" s="30"/>
-      <c r="AC117" s="30"/>
-      <c r="AD117" s="21"/>
-    </row>
-    <row r="118" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="21"/>
-      <c r="B118" s="21"/>
-      <c r="C118" s="21"/>
-      <c r="D118" s="21"/>
-      <c r="E118" s="85"/>
-      <c r="F118" s="85"/>
-      <c r="G118" s="21"/>
-      <c r="H118" s="21"/>
-      <c r="I118" s="21"/>
-      <c r="J118" s="21"/>
-      <c r="K118" s="23"/>
-      <c r="L118" s="85"/>
-      <c r="M118" s="23"/>
-      <c r="N118" s="86"/>
-      <c r="O118" s="23"/>
-      <c r="P118" s="23"/>
-      <c r="Q118" s="23"/>
-      <c r="R118" s="23"/>
-      <c r="S118" s="23"/>
-      <c r="T118" s="23"/>
-      <c r="U118" s="24"/>
-      <c r="V118" s="24"/>
-      <c r="W118" s="88"/>
-      <c r="X118" s="88"/>
-      <c r="Y118" s="88"/>
-      <c r="Z118" s="88"/>
-      <c r="AA118" s="89"/>
-      <c r="AB118" s="30"/>
-      <c r="AC118" s="30"/>
-      <c r="AD118" s="21"/>
-    </row>
-    <row r="119" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="21"/>
-      <c r="B119" s="21"/>
-      <c r="C119" s="21"/>
-      <c r="D119" s="21"/>
-      <c r="E119" s="85"/>
-      <c r="F119" s="85"/>
-      <c r="G119" s="21"/>
-      <c r="H119" s="21"/>
-      <c r="I119" s="21"/>
-      <c r="J119" s="21"/>
-      <c r="K119" s="23"/>
-      <c r="L119" s="85"/>
-      <c r="M119" s="23"/>
-      <c r="N119" s="86"/>
-      <c r="O119" s="23"/>
-      <c r="P119" s="23"/>
-      <c r="Q119" s="23"/>
-      <c r="R119" s="23"/>
-      <c r="S119" s="23"/>
-      <c r="T119" s="23"/>
-      <c r="U119" s="24"/>
-      <c r="V119" s="24"/>
-      <c r="W119" s="88"/>
-      <c r="X119" s="88"/>
-      <c r="Y119" s="88"/>
-      <c r="Z119" s="88"/>
-      <c r="AA119" s="89"/>
-      <c r="AB119" s="30"/>
-      <c r="AC119" s="30"/>
-      <c r="AD119" s="21"/>
-    </row>
-    <row r="120" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="21"/>
-      <c r="B120" s="21"/>
-      <c r="C120" s="21"/>
-      <c r="D120" s="21"/>
-      <c r="E120" s="85"/>
-      <c r="F120" s="85"/>
-      <c r="G120" s="21"/>
-      <c r="H120" s="21"/>
-      <c r="I120" s="21"/>
-      <c r="J120" s="21"/>
-      <c r="K120" s="23"/>
-      <c r="L120" s="85"/>
-      <c r="M120" s="23"/>
-      <c r="N120" s="86"/>
-      <c r="O120" s="23"/>
-      <c r="P120" s="23"/>
-      <c r="Q120" s="23"/>
-      <c r="R120" s="23"/>
-      <c r="S120" s="23"/>
-      <c r="T120" s="23"/>
-      <c r="U120" s="24"/>
-      <c r="V120" s="24"/>
-      <c r="W120" s="88"/>
-      <c r="X120" s="88"/>
-      <c r="Y120" s="88"/>
-      <c r="Z120" s="88"/>
-      <c r="AA120" s="89"/>
-      <c r="AB120" s="30"/>
-      <c r="AC120" s="30"/>
-      <c r="AD120" s="21"/>
-    </row>
-    <row r="121" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="21"/>
-      <c r="B121" s="21"/>
-      <c r="C121" s="21"/>
-      <c r="D121" s="21"/>
-      <c r="E121" s="85"/>
-      <c r="F121" s="85"/>
-      <c r="G121" s="21"/>
-      <c r="H121" s="21"/>
-      <c r="I121" s="21"/>
-      <c r="J121" s="21"/>
-      <c r="K121" s="23"/>
-      <c r="L121" s="85"/>
-      <c r="M121" s="23"/>
-      <c r="N121" s="86"/>
-      <c r="O121" s="23"/>
-      <c r="P121" s="23"/>
-      <c r="Q121" s="23"/>
-      <c r="R121" s="23"/>
-      <c r="S121" s="23"/>
-      <c r="T121" s="23"/>
-      <c r="U121" s="24"/>
-      <c r="V121" s="24"/>
-      <c r="W121" s="88"/>
-      <c r="X121" s="88"/>
-      <c r="Y121" s="88"/>
-      <c r="Z121" s="88"/>
-      <c r="AA121" s="89"/>
-      <c r="AB121" s="30"/>
-      <c r="AC121" s="30"/>
-      <c r="AD121" s="21"/>
-    </row>
-    <row r="122" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="21"/>
-      <c r="B122" s="21"/>
-      <c r="C122" s="21"/>
-      <c r="D122" s="21"/>
-      <c r="E122" s="85"/>
-      <c r="F122" s="85"/>
-      <c r="G122" s="21"/>
-      <c r="H122" s="21"/>
-      <c r="I122" s="21"/>
-      <c r="J122" s="21"/>
-      <c r="K122" s="23"/>
-      <c r="L122" s="85"/>
-      <c r="M122" s="23"/>
-      <c r="N122" s="86"/>
-      <c r="O122" s="23"/>
-      <c r="P122" s="23"/>
-      <c r="Q122" s="23"/>
-      <c r="R122" s="23"/>
-      <c r="S122" s="23"/>
-      <c r="T122" s="23"/>
-      <c r="U122" s="24"/>
-      <c r="V122" s="24"/>
-      <c r="W122" s="88"/>
-      <c r="X122" s="88"/>
-      <c r="Y122" s="88"/>
-      <c r="Z122" s="88"/>
-      <c r="AA122" s="89"/>
-      <c r="AB122" s="30"/>
-      <c r="AC122" s="30"/>
-      <c r="AD122" s="21"/>
-    </row>
-    <row r="123" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="21"/>
-      <c r="B123" s="21"/>
-      <c r="C123" s="21"/>
-      <c r="D123" s="21"/>
-      <c r="E123" s="85"/>
-      <c r="F123" s="85"/>
-      <c r="G123" s="21"/>
-      <c r="H123" s="21"/>
-      <c r="I123" s="21"/>
-      <c r="J123" s="21"/>
-      <c r="K123" s="23"/>
-      <c r="L123" s="85"/>
-      <c r="M123" s="23"/>
-      <c r="N123" s="86"/>
-      <c r="O123" s="23"/>
-      <c r="P123" s="23"/>
-      <c r="Q123" s="23"/>
-      <c r="R123" s="23"/>
-      <c r="S123" s="23"/>
-      <c r="T123" s="23"/>
-      <c r="U123" s="24"/>
-      <c r="V123" s="24"/>
-      <c r="W123" s="88"/>
-      <c r="X123" s="88"/>
-      <c r="Y123" s="88"/>
-      <c r="Z123" s="88"/>
-      <c r="AA123" s="89"/>
-      <c r="AB123" s="30"/>
-      <c r="AC123" s="30"/>
-      <c r="AD123" s="21"/>
-    </row>
-    <row r="124" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="21"/>
-      <c r="B124" s="21"/>
-      <c r="C124" s="21"/>
-      <c r="D124" s="21"/>
-      <c r="E124" s="85"/>
-      <c r="F124" s="85"/>
-      <c r="G124" s="21"/>
-      <c r="H124" s="21"/>
-      <c r="I124" s="21"/>
-      <c r="J124" s="21"/>
-      <c r="K124" s="23"/>
-      <c r="L124" s="85"/>
-      <c r="M124" s="23"/>
-      <c r="N124" s="86"/>
-      <c r="O124" s="23"/>
-      <c r="P124" s="23"/>
-      <c r="Q124" s="23"/>
-      <c r="R124" s="23"/>
-      <c r="S124" s="23"/>
-      <c r="T124" s="23"/>
-      <c r="U124" s="24"/>
-      <c r="V124" s="24"/>
-      <c r="W124" s="88"/>
-      <c r="X124" s="88"/>
-      <c r="Y124" s="88"/>
-      <c r="Z124" s="88"/>
-      <c r="AA124" s="89"/>
-      <c r="AB124" s="30"/>
-      <c r="AC124" s="30"/>
-      <c r="AD124" s="21"/>
-    </row>
-    <row r="125" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="21"/>
-      <c r="B125" s="21"/>
-      <c r="C125" s="21"/>
-      <c r="D125" s="21"/>
-      <c r="E125" s="85"/>
-      <c r="F125" s="85"/>
-      <c r="G125" s="21"/>
-      <c r="H125" s="21"/>
-      <c r="I125" s="21"/>
-      <c r="J125" s="21"/>
-      <c r="K125" s="23"/>
-      <c r="L125" s="85"/>
-      <c r="M125" s="23"/>
-      <c r="N125" s="86"/>
-      <c r="O125" s="23"/>
-      <c r="P125" s="23"/>
-      <c r="Q125" s="23"/>
-      <c r="R125" s="23"/>
-      <c r="S125" s="23"/>
-      <c r="T125" s="23"/>
-      <c r="U125" s="24"/>
-      <c r="V125" s="24"/>
-      <c r="W125" s="88"/>
-      <c r="X125" s="88"/>
-      <c r="Y125" s="88"/>
-      <c r="Z125" s="88"/>
-      <c r="AA125" s="89"/>
-      <c r="AB125" s="30"/>
-      <c r="AC125" s="30"/>
-      <c r="AD125" s="21"/>
-    </row>
-    <row r="126" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="21"/>
-      <c r="B126" s="21"/>
-      <c r="C126" s="21"/>
-      <c r="D126" s="21"/>
-      <c r="E126" s="85"/>
-      <c r="F126" s="85"/>
-      <c r="G126" s="21"/>
-      <c r="H126" s="21"/>
-      <c r="I126" s="21"/>
-      <c r="J126" s="21"/>
-      <c r="K126" s="23"/>
-      <c r="L126" s="85"/>
-      <c r="M126" s="23"/>
-      <c r="N126" s="86"/>
-      <c r="O126" s="23"/>
-      <c r="P126" s="23"/>
-      <c r="Q126" s="23"/>
-      <c r="R126" s="23"/>
-      <c r="S126" s="23"/>
-      <c r="T126" s="23"/>
-      <c r="U126" s="24"/>
-      <c r="V126" s="24"/>
-      <c r="W126" s="88"/>
-      <c r="X126" s="88"/>
-      <c r="Y126" s="88"/>
-      <c r="Z126" s="88"/>
-      <c r="AA126" s="89"/>
-      <c r="AB126" s="30"/>
-      <c r="AC126" s="30"/>
-      <c r="AD126" s="21"/>
-    </row>
-    <row r="127" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="21"/>
-      <c r="B127" s="21"/>
-      <c r="C127" s="21"/>
-      <c r="D127" s="21"/>
-      <c r="E127" s="85"/>
-      <c r="F127" s="85"/>
-      <c r="G127" s="21"/>
-      <c r="H127" s="21"/>
-      <c r="I127" s="21"/>
-      <c r="J127" s="21"/>
-      <c r="K127" s="23"/>
-      <c r="L127" s="85"/>
-      <c r="M127" s="23"/>
-      <c r="N127" s="86"/>
-      <c r="O127" s="23"/>
-      <c r="P127" s="23"/>
-      <c r="Q127" s="23"/>
-      <c r="R127" s="23"/>
-      <c r="S127" s="23"/>
-      <c r="T127" s="23"/>
-      <c r="U127" s="24"/>
-      <c r="V127" s="24"/>
-      <c r="W127" s="88"/>
-      <c r="X127" s="88"/>
-      <c r="Y127" s="88"/>
-      <c r="Z127" s="88"/>
-      <c r="AA127" s="89"/>
-      <c r="AB127" s="30"/>
-      <c r="AC127" s="30"/>
-      <c r="AD127" s="21"/>
-    </row>
-    <row r="128" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="21"/>
-      <c r="B128" s="21"/>
-      <c r="C128" s="21"/>
-      <c r="D128" s="21"/>
-      <c r="E128" s="85"/>
-      <c r="F128" s="85"/>
-      <c r="G128" s="21"/>
-      <c r="H128" s="21"/>
-      <c r="I128" s="21"/>
-      <c r="J128" s="21"/>
-      <c r="K128" s="23"/>
-      <c r="L128" s="85"/>
-      <c r="M128" s="23"/>
-      <c r="N128" s="86"/>
-      <c r="O128" s="23"/>
-      <c r="P128" s="23"/>
-      <c r="Q128" s="23"/>
-      <c r="R128" s="23"/>
-      <c r="S128" s="23"/>
-      <c r="T128" s="23"/>
-      <c r="U128" s="24"/>
-      <c r="V128" s="24"/>
-      <c r="W128" s="88"/>
-      <c r="X128" s="88"/>
-      <c r="Y128" s="88"/>
-      <c r="Z128" s="88"/>
-      <c r="AA128" s="89"/>
-      <c r="AB128" s="30"/>
-      <c r="AC128" s="30"/>
-      <c r="AD128" s="21"/>
-    </row>
-    <row r="129" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="21"/>
-      <c r="B129" s="21"/>
-      <c r="C129" s="21"/>
-      <c r="D129" s="21"/>
-      <c r="E129" s="85"/>
-      <c r="F129" s="85"/>
-      <c r="G129" s="21"/>
-      <c r="H129" s="21"/>
-      <c r="I129" s="21"/>
-      <c r="J129" s="21"/>
-      <c r="K129" s="23"/>
-      <c r="L129" s="85"/>
-      <c r="M129" s="23"/>
-      <c r="N129" s="86"/>
-      <c r="O129" s="23"/>
-      <c r="P129" s="23"/>
-      <c r="Q129" s="23"/>
-      <c r="R129" s="23"/>
-      <c r="S129" s="23"/>
-      <c r="T129" s="23"/>
-      <c r="U129" s="24"/>
-      <c r="V129" s="24"/>
-      <c r="W129" s="88"/>
-      <c r="X129" s="88"/>
-      <c r="Y129" s="88"/>
-      <c r="Z129" s="88"/>
-      <c r="AA129" s="89"/>
-      <c r="AB129" s="30"/>
-      <c r="AC129" s="30"/>
-      <c r="AD129" s="21"/>
-    </row>
-    <row r="130" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="21"/>
-      <c r="B130" s="21"/>
-      <c r="C130" s="21"/>
-      <c r="D130" s="21"/>
-      <c r="E130" s="85"/>
-      <c r="F130" s="85"/>
-      <c r="G130" s="21"/>
-      <c r="H130" s="21"/>
-      <c r="I130" s="21"/>
-      <c r="J130" s="21"/>
-      <c r="K130" s="23"/>
-      <c r="L130" s="85"/>
-      <c r="M130" s="23"/>
-      <c r="N130" s="86"/>
-      <c r="O130" s="23"/>
-      <c r="P130" s="23"/>
-      <c r="Q130" s="23"/>
-      <c r="R130" s="23"/>
-      <c r="S130" s="23"/>
-      <c r="T130" s="23"/>
-      <c r="U130" s="24"/>
-      <c r="V130" s="24"/>
-      <c r="W130" s="88"/>
-      <c r="X130" s="88"/>
-      <c r="Y130" s="88"/>
-      <c r="Z130" s="88"/>
-      <c r="AA130" s="89"/>
-      <c r="AB130" s="30"/>
-      <c r="AC130" s="30"/>
-      <c r="AD130" s="21"/>
-    </row>
-    <row r="131" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="21"/>
-      <c r="B131" s="21"/>
-      <c r="C131" s="21"/>
-      <c r="D131" s="21"/>
-      <c r="E131" s="85"/>
-      <c r="F131" s="85"/>
-      <c r="G131" s="21"/>
-      <c r="H131" s="21"/>
-      <c r="I131" s="21"/>
-      <c r="J131" s="21"/>
-      <c r="K131" s="23"/>
-      <c r="L131" s="85"/>
-      <c r="M131" s="23"/>
-      <c r="N131" s="86"/>
-      <c r="O131" s="23"/>
-      <c r="P131" s="23"/>
-      <c r="Q131" s="23"/>
-      <c r="R131" s="23"/>
-      <c r="S131" s="23"/>
-      <c r="T131" s="23"/>
-      <c r="U131" s="24"/>
-      <c r="V131" s="24"/>
-      <c r="W131" s="88"/>
-      <c r="X131" s="88"/>
-      <c r="Y131" s="88"/>
-      <c r="Z131" s="88"/>
-      <c r="AA131" s="89"/>
-      <c r="AB131" s="30"/>
-      <c r="AC131" s="30"/>
-      <c r="AD131" s="21"/>
-    </row>
-    <row r="132" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="21"/>
-      <c r="B132" s="21"/>
-      <c r="C132" s="21"/>
-      <c r="D132" s="21"/>
-      <c r="E132" s="85"/>
-      <c r="F132" s="85"/>
-      <c r="G132" s="21"/>
-      <c r="H132" s="21"/>
-      <c r="I132" s="21"/>
-      <c r="J132" s="21"/>
-      <c r="K132" s="23"/>
-      <c r="L132" s="85"/>
-      <c r="M132" s="23"/>
-      <c r="N132" s="86"/>
-      <c r="O132" s="23"/>
-      <c r="P132" s="23"/>
-      <c r="Q132" s="23"/>
-      <c r="R132" s="23"/>
-      <c r="S132" s="23"/>
-      <c r="T132" s="23"/>
-      <c r="U132" s="24"/>
-      <c r="V132" s="24"/>
-      <c r="W132" s="88"/>
-      <c r="X132" s="88"/>
-      <c r="Y132" s="88"/>
-      <c r="Z132" s="88"/>
-      <c r="AA132" s="89"/>
-      <c r="AB132" s="30"/>
-      <c r="AC132" s="30"/>
-      <c r="AD132" s="21"/>
-    </row>
-    <row r="133" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="21"/>
-      <c r="B133" s="21"/>
-      <c r="C133" s="21"/>
-      <c r="D133" s="21"/>
-      <c r="E133" s="85"/>
-      <c r="F133" s="85"/>
-      <c r="G133" s="21"/>
-      <c r="H133" s="21"/>
-      <c r="I133" s="21"/>
-      <c r="J133" s="21"/>
-      <c r="K133" s="23"/>
-      <c r="L133" s="85"/>
-      <c r="M133" s="23"/>
-      <c r="N133" s="86"/>
-      <c r="O133" s="23"/>
-      <c r="P133" s="23"/>
-      <c r="Q133" s="23"/>
-      <c r="R133" s="23"/>
-      <c r="S133" s="23"/>
-      <c r="T133" s="23"/>
-      <c r="U133" s="24"/>
-      <c r="V133" s="24"/>
-      <c r="W133" s="88"/>
-      <c r="X133" s="88"/>
-      <c r="Y133" s="88"/>
-      <c r="Z133" s="88"/>
-      <c r="AA133" s="89"/>
-      <c r="AB133" s="30"/>
-      <c r="AC133" s="30"/>
-      <c r="AD133" s="21"/>
-    </row>
-    <row r="134" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="21"/>
-      <c r="B134" s="21"/>
-      <c r="C134" s="21"/>
-      <c r="D134" s="21"/>
-      <c r="E134" s="85"/>
-      <c r="F134" s="85"/>
-      <c r="G134" s="21"/>
-      <c r="H134" s="21"/>
-      <c r="I134" s="21"/>
-      <c r="J134" s="21"/>
-      <c r="K134" s="23"/>
-      <c r="L134" s="85"/>
-      <c r="M134" s="23"/>
-      <c r="N134" s="86"/>
-      <c r="O134" s="23"/>
-      <c r="P134" s="23"/>
-      <c r="Q134" s="23"/>
-      <c r="R134" s="23"/>
-      <c r="S134" s="23"/>
-      <c r="T134" s="23"/>
-      <c r="U134" s="24"/>
-      <c r="V134" s="24"/>
-      <c r="W134" s="88"/>
-      <c r="X134" s="88"/>
-      <c r="Y134" s="88"/>
-      <c r="Z134" s="88"/>
-      <c r="AA134" s="89"/>
-      <c r="AB134" s="30"/>
-      <c r="AC134" s="30"/>
-      <c r="AD134" s="21"/>
-    </row>
-    <row r="135" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="21"/>
-      <c r="B135" s="21"/>
-      <c r="C135" s="21"/>
-      <c r="D135" s="21"/>
-      <c r="E135" s="85"/>
-      <c r="F135" s="85"/>
-      <c r="G135" s="21"/>
-      <c r="H135" s="21"/>
-      <c r="I135" s="21"/>
-      <c r="J135" s="21"/>
-      <c r="K135" s="23"/>
-      <c r="L135" s="85"/>
-      <c r="M135" s="23"/>
-      <c r="N135" s="86"/>
-      <c r="O135" s="23"/>
-      <c r="P135" s="23"/>
-      <c r="Q135" s="23"/>
-      <c r="R135" s="23"/>
-      <c r="S135" s="23"/>
-      <c r="T135" s="23"/>
-      <c r="U135" s="24"/>
-      <c r="V135" s="24"/>
-      <c r="W135" s="88"/>
-      <c r="X135" s="88"/>
-      <c r="Y135" s="88"/>
-      <c r="Z135" s="88"/>
-      <c r="AA135" s="89"/>
-      <c r="AB135" s="30"/>
-      <c r="AC135" s="30"/>
-      <c r="AD135" s="21"/>
-    </row>
-    <row r="136" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="21"/>
-      <c r="B136" s="21"/>
-      <c r="C136" s="21"/>
-      <c r="D136" s="21"/>
-      <c r="E136" s="85"/>
-      <c r="F136" s="85"/>
-      <c r="G136" s="21"/>
-      <c r="H136" s="21"/>
-      <c r="I136" s="21"/>
-      <c r="J136" s="21"/>
-      <c r="K136" s="23"/>
-      <c r="L136" s="85"/>
-      <c r="M136" s="23"/>
-      <c r="N136" s="86"/>
-      <c r="O136" s="23"/>
-      <c r="P136" s="23"/>
-      <c r="Q136" s="23"/>
-      <c r="R136" s="23"/>
-      <c r="S136" s="23"/>
-      <c r="T136" s="23"/>
-      <c r="U136" s="24"/>
-      <c r="V136" s="24"/>
-      <c r="W136" s="88"/>
-      <c r="X136" s="88"/>
-      <c r="Y136" s="88"/>
-      <c r="Z136" s="88"/>
-      <c r="AA136" s="89"/>
-      <c r="AB136" s="30"/>
-      <c r="AC136" s="30"/>
-      <c r="AD136" s="21"/>
-    </row>
-    <row r="137" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="21"/>
-      <c r="B137" s="21"/>
-      <c r="C137" s="21"/>
-      <c r="D137" s="21"/>
-      <c r="E137" s="85"/>
-      <c r="F137" s="85"/>
-      <c r="G137" s="21"/>
-      <c r="H137" s="21"/>
-      <c r="I137" s="21"/>
-      <c r="J137" s="21"/>
-      <c r="K137" s="23"/>
-      <c r="L137" s="85"/>
-      <c r="M137" s="23"/>
-      <c r="N137" s="86"/>
-      <c r="O137" s="23"/>
-      <c r="P137" s="23"/>
-      <c r="Q137" s="23"/>
-      <c r="R137" s="23"/>
-      <c r="S137" s="23"/>
-      <c r="T137" s="23"/>
-      <c r="U137" s="24"/>
-      <c r="V137" s="24"/>
-      <c r="W137" s="88"/>
-      <c r="X137" s="88"/>
-      <c r="Y137" s="88"/>
-      <c r="Z137" s="88"/>
-      <c r="AA137" s="89"/>
-      <c r="AB137" s="30"/>
-      <c r="AC137" s="30"/>
-      <c r="AD137" s="21"/>
-    </row>
-    <row r="138" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="21"/>
-      <c r="B138" s="21"/>
-      <c r="C138" s="21"/>
-      <c r="D138" s="21"/>
-      <c r="E138" s="85"/>
-      <c r="F138" s="85"/>
-      <c r="G138" s="21"/>
-      <c r="H138" s="21"/>
-      <c r="I138" s="21"/>
-      <c r="J138" s="21"/>
-      <c r="K138" s="23"/>
-      <c r="L138" s="85"/>
-      <c r="M138" s="23"/>
-      <c r="N138" s="86"/>
-      <c r="O138" s="23"/>
-      <c r="P138" s="23"/>
-      <c r="Q138" s="23"/>
-      <c r="R138" s="23"/>
-      <c r="S138" s="23"/>
-      <c r="T138" s="23"/>
-      <c r="U138" s="24"/>
-      <c r="V138" s="24"/>
-      <c r="W138" s="88"/>
-      <c r="X138" s="88"/>
-      <c r="Y138" s="88"/>
-      <c r="Z138" s="88"/>
-      <c r="AA138" s="89"/>
-      <c r="AB138" s="30"/>
-      <c r="AC138" s="30"/>
-      <c r="AD138" s="21"/>
-    </row>
-    <row r="139" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="21"/>
-      <c r="B139" s="21"/>
-      <c r="C139" s="21"/>
-      <c r="D139" s="21"/>
-      <c r="E139" s="85"/>
-      <c r="F139" s="85"/>
-      <c r="G139" s="21"/>
-      <c r="H139" s="21"/>
-      <c r="I139" s="21"/>
-      <c r="J139" s="21"/>
-      <c r="K139" s="23"/>
-      <c r="L139" s="85"/>
-      <c r="M139" s="23"/>
-      <c r="N139" s="86"/>
-      <c r="O139" s="23"/>
-      <c r="P139" s="23"/>
-      <c r="Q139" s="23"/>
-      <c r="R139" s="23"/>
-      <c r="S139" s="23"/>
-      <c r="T139" s="23"/>
-      <c r="U139" s="24"/>
-      <c r="V139" s="24"/>
-      <c r="W139" s="88"/>
-      <c r="X139" s="88"/>
-      <c r="Y139" s="88"/>
-      <c r="Z139" s="88"/>
-      <c r="AA139" s="89"/>
-      <c r="AB139" s="30"/>
-      <c r="AC139" s="30"/>
-      <c r="AD139" s="21"/>
-    </row>
-    <row r="140" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="21"/>
-      <c r="B140" s="21"/>
-      <c r="C140" s="21"/>
-      <c r="D140" s="21"/>
-      <c r="E140" s="85"/>
-      <c r="F140" s="85"/>
-      <c r="G140" s="21"/>
-      <c r="H140" s="21"/>
-      <c r="I140" s="21"/>
-      <c r="J140" s="21"/>
-      <c r="K140" s="23"/>
-      <c r="L140" s="85"/>
-      <c r="M140" s="23"/>
-      <c r="N140" s="86"/>
-      <c r="O140" s="23"/>
-      <c r="P140" s="23"/>
-      <c r="Q140" s="23"/>
-      <c r="R140" s="23"/>
-      <c r="S140" s="23"/>
-      <c r="T140" s="23"/>
-      <c r="U140" s="24"/>
-      <c r="V140" s="24"/>
-      <c r="W140" s="88"/>
-      <c r="X140" s="88"/>
-      <c r="Y140" s="88"/>
-      <c r="Z140" s="88"/>
-      <c r="AA140" s="89"/>
-      <c r="AB140" s="30"/>
-      <c r="AC140" s="30"/>
-      <c r="AD140" s="21"/>
-    </row>
-    <row r="141" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="21"/>
-      <c r="B141" s="21"/>
-      <c r="C141" s="21"/>
-      <c r="D141" s="21"/>
-      <c r="E141" s="85"/>
-      <c r="F141" s="85"/>
-      <c r="G141" s="21"/>
-      <c r="H141" s="21"/>
-      <c r="I141" s="21"/>
-      <c r="J141" s="21"/>
-      <c r="K141" s="23"/>
-      <c r="L141" s="85"/>
-      <c r="M141" s="23"/>
-      <c r="N141" s="86"/>
-      <c r="O141" s="23"/>
-      <c r="P141" s="23"/>
-      <c r="Q141" s="23"/>
-      <c r="R141" s="23"/>
-      <c r="S141" s="23"/>
-      <c r="T141" s="23"/>
-      <c r="U141" s="24"/>
-      <c r="V141" s="24"/>
-      <c r="W141" s="88"/>
-      <c r="X141" s="88"/>
-      <c r="Y141" s="88"/>
-      <c r="Z141" s="88"/>
-      <c r="AA141" s="89"/>
-      <c r="AB141" s="30"/>
-      <c r="AC141" s="30"/>
-      <c r="AD141" s="21"/>
-    </row>
-    <row r="142" spans="1:30" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="21"/>
-      <c r="B142" s="21"/>
-      <c r="C142" s="21"/>
-      <c r="D142" s="21"/>
-      <c r="E142" s="85"/>
-      <c r="F142" s="85"/>
-      <c r="G142" s="21"/>
-      <c r="H142" s="21"/>
-      <c r="I142" s="21"/>
-      <c r="J142" s="21"/>
-      <c r="K142" s="23"/>
-      <c r="L142" s="85"/>
-      <c r="M142" s="23"/>
-      <c r="N142" s="86"/>
-      <c r="O142" s="23"/>
-      <c r="P142" s="23"/>
-      <c r="Q142" s="23"/>
-      <c r="R142" s="23"/>
-      <c r="S142" s="23"/>
-      <c r="T142" s="23"/>
-      <c r="U142" s="24"/>
-      <c r="V142" s="24"/>
-      <c r="W142" s="88"/>
-      <c r="X142" s="88"/>
-      <c r="Y142" s="88"/>
-      <c r="Z142" s="88"/>
-      <c r="AA142" s="89"/>
-      <c r="AB142" s="30"/>
-      <c r="AC142" s="30"/>
-      <c r="AD142" s="21"/>
-    </row>
-    <row r="143" spans="1:30" ht="29.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="1:30" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="42" t="s">
+    <row r="49" spans="1:29" ht="29.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="1:29" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="42" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="145" spans="1:29" ht="24.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="90" t="s">
+    <row r="51" spans="1:29" ht="24.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="B146" s="90"/>
-      <c r="AC146" s="27"/>
-    </row>
-    <row r="147" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AC147" s="28"/>
-    </row>
-    <row r="148" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AC148" s="29"/>
-    </row>
-    <row r="150" spans="1:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="1:29" ht="48.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="1:29" ht="43.35" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="1:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B52" s="90"/>
+      <c r="AC52" s="27"/>
+    </row>
+    <row r="53" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC53" s="28"/>
+    </row>
+    <row r="54" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC54" s="29"/>
+    </row>
+    <row r="56" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="1:29" ht="48.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="1:29" ht="43.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <sheetProtection formatRows="0" insertRows="0" deleteRows="0"/>
   <mergeCells count="8">
-    <mergeCell ref="A146:B146"/>
+    <mergeCell ref="A52:B52"/>
     <mergeCell ref="AB7:AC7"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="H5:I5"/>
@@ -6509,16 +3501,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9:H142" xr:uid="{15F26528-5832-4F2D-A959-9BB429F166D8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9:H48" xr:uid="{15F26528-5832-4F2D-A959-9BB429F166D8}">
       <formula1>"M,F"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I9:I142" xr:uid="{22C651AA-9BBA-492F-846F-230D00E1A53F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I9:I48" xr:uid="{22C651AA-9BBA-492F-846F-230D00E1A53F}">
       <formula1>"C,I,M,O"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9:D142" xr:uid="{AD9A9387-6DA5-4014-84BE-5031F23D692C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9:D48" xr:uid="{AD9A9387-6DA5-4014-84BE-5031F23D692C}">
       <formula1>"SC,PR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M9:N142" xr:uid="{FE4BC584-575F-4F90-B320-55B0AA605F28}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M9:N48" xr:uid="{FE4BC584-575F-4F90-B320-55B0AA605F28}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -6531,67 +3523,67 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0343722D-AEEE-49CD-A89E-34E0E3A5CD7F}">
   <dimension ref="A1:J109"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="44" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" style="43" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" style="44" customWidth="1"/>
-    <col min="4" max="6" width="20.85546875" style="44" customWidth="1"/>
-    <col min="7" max="7" width="44.85546875" style="43" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.85546875" style="43" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="44"/>
+    <col min="1" max="1" width="3.5" style="44" customWidth="1"/>
+    <col min="2" max="2" width="6.1640625" style="43" customWidth="1"/>
+    <col min="3" max="3" width="41.83203125" style="44" customWidth="1"/>
+    <col min="4" max="6" width="20.83203125" style="44" customWidth="1"/>
+    <col min="7" max="7" width="44.83203125" style="43" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.83203125" style="43" customWidth="1"/>
+    <col min="9" max="16384" width="9.1640625" style="44"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.2">
       <c r="F1" s="45"/>
     </row>
-    <row r="2" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="112" t="s">
+    <row r="2" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="112"/>
+      <c r="C2" s="101"/>
       <c r="D2" s="45" t="s">
         <v>49</v>
       </c>
       <c r="E2" s="45"/>
     </row>
-    <row r="3" spans="2:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="46"/>
       <c r="C3" s="46"/>
       <c r="D3" s="46"/>
       <c r="E3" s="46"/>
     </row>
-    <row r="4" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="46"/>
       <c r="C4" s="46"/>
       <c r="D4" s="46"/>
       <c r="E4" s="47"/>
       <c r="F4" s="47"/>
     </row>
-    <row r="5" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="2:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="113" t="s">
+    <row r="5" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="2:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="102" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
-      <c r="F10" s="113"/>
-      <c r="G10" s="113"/>
-      <c r="H10" s="113"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
       <c r="I10" s="48"/>
       <c r="J10" s="48"/>
     </row>
-    <row r="11" spans="2:10" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="112" t="s">
+    <row r="11" spans="2:10" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="112"/>
+      <c r="C12" s="101"/>
       <c r="D12" s="49" t="s">
         <v>52</v>
       </c>
@@ -6604,29 +3596,29 @@
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
     </row>
-    <row r="14" spans="2:10" s="50" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="107" t="s">
+    <row r="14" spans="2:10" s="50" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="108"/>
-      <c r="D14" s="108"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="109"/>
-    </row>
-    <row r="15" spans="2:10" s="50" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="114" t="s">
+      <c r="C14" s="104"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="105"/>
+    </row>
+    <row r="15" spans="2:10" s="50" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="115"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="115"/>
-      <c r="G15" s="115"/>
-      <c r="H15" s="116"/>
-    </row>
-    <row r="16" spans="2:10" s="50" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="107"/>
+      <c r="D15" s="107"/>
+      <c r="E15" s="107"/>
+      <c r="F15" s="107"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="108"/>
+    </row>
+    <row r="16" spans="2:10" s="50" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="51"/>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
@@ -6635,14 +3627,14 @@
       <c r="G16" s="52"/>
       <c r="H16" s="52"/>
     </row>
-    <row r="17" spans="2:10" s="50" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="111" t="s">
+    <row r="17" spans="2:10" s="50" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="100" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="111"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="111"/>
-      <c r="F17" s="111"/>
+      <c r="C17" s="100"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="100"/>
       <c r="G17" s="53" t="s">
         <v>57</v>
       </c>
@@ -6650,140 +3642,140 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="2:10" s="50" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="107" t="s">
+    <row r="18" spans="2:10" s="50" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="108"/>
-      <c r="D18" s="108"/>
-      <c r="E18" s="108"/>
-      <c r="F18" s="108"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="109"/>
-    </row>
-    <row r="19" spans="2:10" s="50" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="104"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="105"/>
+    </row>
+    <row r="19" spans="2:10" s="50" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="55">
         <v>1</v>
       </c>
-      <c r="C19" s="100" t="s">
+      <c r="C19" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="101"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="101"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="110"/>
+      <c r="F19" s="110"/>
       <c r="G19" s="56"/>
       <c r="H19" s="57"/>
     </row>
-    <row r="20" spans="2:10" s="50" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" s="50" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="55">
         <v>2</v>
       </c>
-      <c r="C20" s="100" t="s">
+      <c r="C20" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="101"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="101"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="110"/>
       <c r="G20" s="56"/>
       <c r="H20" s="57"/>
     </row>
-    <row r="21" spans="2:10" s="50" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" s="50" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="55">
         <v>3</v>
       </c>
-      <c r="C21" s="100" t="s">
+      <c r="C21" s="109" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="101"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="102"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="111"/>
       <c r="H21" s="57"/>
     </row>
-    <row r="22" spans="2:10" s="50" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" s="50" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="55">
         <v>4</v>
       </c>
-      <c r="C22" s="110" t="s">
+      <c r="C22" s="116" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="110"/>
-      <c r="E22" s="110"/>
-      <c r="F22" s="110"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="116"/>
+      <c r="F22" s="116"/>
       <c r="G22" s="56"/>
       <c r="H22" s="57"/>
     </row>
-    <row r="23" spans="2:10" s="50" customFormat="1" ht="58.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" s="50" customFormat="1" ht="58.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="55">
         <v>5</v>
       </c>
-      <c r="C23" s="110" t="s">
+      <c r="C23" s="116" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="110"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="110"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="116"/>
+      <c r="F23" s="116"/>
       <c r="G23" s="56"/>
       <c r="H23" s="57"/>
     </row>
-    <row r="24" spans="2:10" ht="50.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" ht="50.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="55">
         <v>6</v>
       </c>
-      <c r="C24" s="100" t="s">
+      <c r="C24" s="109" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="101"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="102"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="111"/>
       <c r="G24" s="55"/>
       <c r="H24" s="55"/>
     </row>
-    <row r="25" spans="2:10" ht="50.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" ht="50.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="55">
         <v>7</v>
       </c>
-      <c r="C25" s="100" t="s">
+      <c r="C25" s="109" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="101"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="102"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="111"/>
       <c r="G25" s="58"/>
       <c r="H25" s="58"/>
       <c r="I25" s="59"/>
       <c r="J25" s="60"/>
     </row>
-    <row r="26" spans="2:10" ht="60.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" ht="61" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="55">
         <v>8</v>
       </c>
-      <c r="C26" s="103" t="s">
+      <c r="C26" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="104"/>
-      <c r="E26" s="104"/>
-      <c r="F26" s="105"/>
+      <c r="D26" s="113"/>
+      <c r="E26" s="113"/>
+      <c r="F26" s="114"/>
       <c r="G26" s="61"/>
       <c r="H26" s="62"/>
       <c r="I26" s="59"/>
       <c r="J26" s="60"/>
     </row>
-    <row r="27" spans="2:10" ht="110.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" ht="110" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="63">
         <v>9</v>
       </c>
-      <c r="C27" s="106" t="s">
+      <c r="C27" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="106"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="106"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
       <c r="G27" s="64"/>
       <c r="H27" s="65"/>
       <c r="I27" s="59"/>
       <c r="J27" s="60"/>
     </row>
-    <row r="28" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="44"/>
       <c r="D28" s="66"/>
       <c r="G28" s="67"/>
@@ -6791,36 +3783,36 @@
       <c r="I28" s="68"/>
       <c r="J28" s="60"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29" s="44"/>
       <c r="G29" s="44"/>
       <c r="H29" s="44"/>
       <c r="I29" s="69"/>
       <c r="J29" s="60"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="44"/>
       <c r="G30" s="44"/>
       <c r="H30" s="44"/>
       <c r="I30" s="70"/>
       <c r="J30" s="60"/>
     </row>
-    <row r="83" spans="1:7" ht="18.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="84" spans="1:7" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" ht="19" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:7" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="71"/>
       <c r="B84" s="72"/>
       <c r="C84" s="73"/>
       <c r="D84" s="73"/>
       <c r="E84" s="74"/>
     </row>
-    <row r="90" spans="1:7" s="43" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" s="43" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="44"/>
       <c r="C90" s="44"/>
       <c r="D90" s="44"/>
       <c r="E90" s="44"/>
       <c r="F90" s="44"/>
     </row>
-    <row r="91" spans="1:7" s="43" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" s="43" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A91" s="44"/>
       <c r="C91" s="44"/>
       <c r="D91" s="44"/>
@@ -6828,7 +3820,7 @@
       <c r="F91" s="75"/>
       <c r="G91" s="76"/>
     </row>
-    <row r="92" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="77"/>
       <c r="B92" s="78"/>
       <c r="C92" s="75"/>
@@ -6837,7 +3829,7 @@
       <c r="F92" s="75"/>
       <c r="G92" s="76"/>
     </row>
-    <row r="93" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A93" s="79"/>
       <c r="C93" s="44"/>
       <c r="D93" s="44"/>
@@ -6845,7 +3837,7 @@
       <c r="F93" s="44"/>
       <c r="G93" s="80"/>
     </row>
-    <row r="94" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="79"/>
       <c r="C94" s="44"/>
       <c r="D94" s="44"/>
@@ -6853,7 +3845,7 @@
       <c r="F94" s="44"/>
       <c r="G94" s="80"/>
     </row>
-    <row r="95" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="79"/>
       <c r="C95" s="44"/>
       <c r="D95" s="44"/>
@@ -6861,7 +3853,7 @@
       <c r="F95" s="44"/>
       <c r="G95" s="80"/>
     </row>
-    <row r="96" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="79"/>
       <c r="C96" s="44"/>
       <c r="D96" s="44"/>
@@ -6869,7 +3861,7 @@
       <c r="F96" s="44"/>
       <c r="G96" s="80"/>
     </row>
-    <row r="97" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="79"/>
       <c r="C97" s="44"/>
       <c r="D97" s="44"/>
@@ -6877,7 +3869,7 @@
       <c r="F97" s="44"/>
       <c r="G97" s="80"/>
     </row>
-    <row r="98" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="79"/>
       <c r="C98" s="44"/>
       <c r="D98" s="44"/>
@@ -6885,7 +3877,7 @@
       <c r="F98" s="44"/>
       <c r="G98" s="80"/>
     </row>
-    <row r="99" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A99" s="79"/>
       <c r="C99" s="44"/>
       <c r="D99" s="44"/>
@@ -6893,7 +3885,7 @@
       <c r="F99" s="44"/>
       <c r="G99" s="80"/>
     </row>
-    <row r="100" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="79"/>
       <c r="C100" s="44"/>
       <c r="D100" s="44"/>
@@ -6901,7 +3893,7 @@
       <c r="F100" s="44"/>
       <c r="G100" s="80"/>
     </row>
-    <row r="101" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="79"/>
       <c r="C101" s="44"/>
       <c r="D101" s="44"/>
@@ -6909,7 +3901,7 @@
       <c r="F101" s="44"/>
       <c r="G101" s="80"/>
     </row>
-    <row r="102" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A102" s="79"/>
       <c r="C102" s="44"/>
       <c r="D102" s="44"/>
@@ -6917,7 +3909,7 @@
       <c r="F102" s="44"/>
       <c r="G102" s="80"/>
     </row>
-    <row r="103" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A103" s="79"/>
       <c r="C103" s="44"/>
       <c r="D103" s="44"/>
@@ -6925,7 +3917,7 @@
       <c r="F103" s="44"/>
       <c r="G103" s="80"/>
     </row>
-    <row r="104" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="79"/>
       <c r="C104" s="44"/>
       <c r="D104" s="44"/>
@@ -6933,7 +3925,7 @@
       <c r="F104" s="44"/>
       <c r="G104" s="80"/>
     </row>
-    <row r="105" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A105" s="79"/>
       <c r="C105" s="44"/>
       <c r="D105" s="44"/>
@@ -6941,7 +3933,7 @@
       <c r="F105" s="44"/>
       <c r="G105" s="80"/>
     </row>
-    <row r="106" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="79"/>
       <c r="C106" s="44"/>
       <c r="D106" s="44"/>
@@ -6949,7 +3941,7 @@
       <c r="F106" s="44"/>
       <c r="G106" s="80"/>
     </row>
-    <row r="107" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="79"/>
       <c r="C107" s="44"/>
       <c r="D107" s="44"/>
@@ -6957,7 +3949,7 @@
       <c r="F107" s="44"/>
       <c r="G107" s="80"/>
     </row>
-    <row r="108" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="79"/>
       <c r="C108" s="44"/>
       <c r="D108" s="44"/>
@@ -6965,7 +3957,7 @@
       <c r="F108" s="44"/>
       <c r="G108" s="80"/>
     </row>
-    <row r="109" spans="1:7" s="43" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" s="43" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A109" s="81"/>
       <c r="B109" s="82"/>
       <c r="C109" s="83"/>
@@ -6976,12 +3968,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B15:H15"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C26:F26"/>
@@ -6992,6 +3978,12 @@
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C23:F23"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B15:H15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7001,54 +3993,54 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{917ED85D-4CC0-4DC1-ACC9-E45FFA04D12E}">
   <dimension ref="A3:A15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>73</v>
       </c>
